--- a/src/attributions/attributions_saliency_traj_472.xlsx
+++ b/src/attributions/attributions_saliency_traj_472.xlsx
@@ -2137,571 +2137,571 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0005347459809854627</v>
+        <v>8.736122936170432e-10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.009344153106212616</v>
+        <v>1.718308828557724e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00140873622149229</v>
+        <v>2.996123904530634e-10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001898689661175013</v>
+        <v>1.249868541997046e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001911995816044509</v>
+        <v>8.888566549458687e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000127497361972928</v>
+        <v>5.326696861374103e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001485559507273138</v>
+        <v>8.4614326656407e-10</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0006853323429822922</v>
+        <v>1.418873685210542e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002380267949774861</v>
+        <v>5.18728338061436e-10</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001953570870682597</v>
+        <v>8.082868818704014e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008168214932084084</v>
+        <v>2.153434319751568e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001377194654196501</v>
+        <v>8.288898456498828e-10</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003226307220757008</v>
+        <v>1.483693390369467e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002624931978061795</v>
+        <v>6.962004861499338e-10</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001731678028590977</v>
+        <v>9.143961143820434e-10</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001229211105965078</v>
+        <v>1.786156333949407e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005531922215595841</v>
+        <v>1.64421698478634e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001936748973093927</v>
+        <v>1.826953310857249e-10</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0009540654136799276</v>
+        <v>5.027039895466601e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001337426598183811</v>
+        <v>4.551981291900375e-10</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0004379162273835391</v>
+        <v>7.251656219953162e-11</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003858167328871787</v>
+        <v>6.366848159800043e-10</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001192330499179661</v>
+        <v>1.599886612080326e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001120002474635839</v>
+        <v>2.637354779011503e-10</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001455975143471733</v>
+        <v>3.956640293178992e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008685347274877131</v>
+        <v>3.222174471684269e-10</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0009829625487327576</v>
+        <v>9.261879596600409e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0008586545009166002</v>
+        <v>1.751858991205779e-09</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0009352407651022077</v>
+        <v>1.06428255097768e-09</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.001174468430690467</v>
+        <v>7.111988220565024e-10</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0003494034463074058</v>
+        <v>3.98124255784893e-10</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0005982615402899683</v>
+        <v>6.721618817095987e-10</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0002321788924746215</v>
+        <v>1.653343434382393e-10</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0003874754183925688</v>
+        <v>9.1450597095033e-12</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001440726104192436</v>
+        <v>5.128512614582803e-10</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0001971332385437563</v>
+        <v>5.152810400588237e-10</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0008540531853213906</v>
+        <v>2.678948174406059e-10</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0008241767063736916</v>
+        <v>3.315738794640311e-10</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0001588011073181406</v>
+        <v>4.374796080952592e-10</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.000363719038432464</v>
+        <v>6.299003540988224e-10</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.347350917058066e-05</v>
+        <v>5.261814872703496e-10</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0004180189280305058</v>
+        <v>1.000918931071126e-10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0001147277289419435</v>
+        <v>6.493044435451623e-10</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.752225216478109e-05</v>
+        <v>2.451078784382332e-10</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0002551429788582027</v>
+        <v>2.467585580312459e-10</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0008324311929754913</v>
+        <v>4.451857771314849e-10</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.005580901633948088</v>
+        <v>2.90680646219954e-10</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001045926939696074</v>
+        <v>8.65869764776761e-10</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001118977903388441</v>
+        <v>3.859653707749544e-10</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0005204660119488835</v>
+        <v>9.515033205786949e-10</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0001423031790181994</v>
+        <v>5.508720701818959e-10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.002094764029607177</v>
+        <v>6.821151421476657e-10</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.000296387413982302</v>
+        <v>1.074711764026404e-09</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.000155691581312567</v>
+        <v>2.479327021465139e-10</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.471341475844383e-05</v>
+        <v>1.37199474004035e-10</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.003813369898125529</v>
+        <v>3.073999388369941e-11</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002567010698840022</v>
+        <v>6.976966226979187e-10</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0009059446747414768</v>
+        <v>2.818735245213588e-10</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.00141061982139945</v>
+        <v>1.132128946146338e-09</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0006164180231280625</v>
+        <v>4.462785696546234e-10</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0008328820113092661</v>
+        <v>1.61331309422863e-10</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0004977654898539186</v>
+        <v>1.684117775790916e-11</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0001331910898443311</v>
+        <v>1.795385173863906e-09</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0001843632635427639</v>
+        <v>4.534797537480983e-10</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.121581150684506e-05</v>
+        <v>9.382594701179414e-10</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.001078101806342602</v>
+        <v>4.487576976686114e-10</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0003086687065660954</v>
+        <v>3.705970252898538e-11</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002385025843977928</v>
+        <v>9.341675211160805e-10</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0007885260274633765</v>
+        <v>1.468457161424297e-10</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.000665338768158108</v>
+        <v>2.198104198658513e-10</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001643320312723517</v>
+        <v>7.155659398350167e-11</v>
       </c>
       <c r="BT4" t="n">
-        <v>3.868143539875746e-05</v>
+        <v>1.559776474646668e-10</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0001451318094041198</v>
+        <v>4.935941100292496e-10</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.002377622062340379</v>
+        <v>3.625232614101748e-10</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0008640269516035914</v>
+        <v>7.457953699052666e-11</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0004019818443339318</v>
+        <v>2.971368984194811e-11</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0005158478743396699</v>
+        <v>7.026308423974115e-10</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7.779522275086492e-05</v>
+        <v>5.549492532175293e-10</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0007181584951467812</v>
+        <v>1.103876434704887e-09</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0008523390861228108</v>
+        <v>3.051748437288282e-11</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0001077436900231987</v>
+        <v>4.684888241235363e-11</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0001207043023896404</v>
+        <v>1.286523942933826e-10</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001677386811934412</v>
+        <v>2.624058470512836e-10</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0006569349789060652</v>
+        <v>2.515763153354555e-10</v>
       </c>
       <c r="CG4" t="n">
-        <v>9.501887689111754e-05</v>
+        <v>5.029875127515737e-11</v>
       </c>
       <c r="CH4" t="n">
-        <v>3.068562364205718e-05</v>
+        <v>1.709853370002179e-10</v>
       </c>
       <c r="CI4" t="n">
-        <v>5.182038876228034e-06</v>
+        <v>9.909219278458892e-11</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0004427946114446968</v>
+        <v>2.037804092136497e-10</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0002059012622339651</v>
+        <v>1.345972500121917e-10</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0004937582416459918</v>
+        <v>6.508840688645989e-11</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001724534900858998</v>
+        <v>7.324911233119735e-10</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.00191483972594142</v>
+        <v>5.371307287838079e-10</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0002020244719460607</v>
+        <v>5.465988772712649e-10</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.002077191835269332</v>
+        <v>1.144295769250903e-11</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002250361256301403</v>
+        <v>9.292414615558187e-10</v>
       </c>
       <c r="CR4" t="n">
-        <v>3.71196074411273e-06</v>
+        <v>7.972813520495947e-10</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.00037645164411515</v>
+        <v>2.667238652165338e-10</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0004521849332377315</v>
+        <v>9.285935353986474e-10</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.001123017398640513</v>
+        <v>7.447918393133079e-10</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0001774720585672185</v>
+        <v>9.989968574597441e-11</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.001507947919890285</v>
+        <v>4.233092210093048e-10</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0006263329996727407</v>
+        <v>2.433414025837521e-10</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0004457102913875133</v>
+        <v>1.177644926020349e-10</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0003034255059901625</v>
+        <v>1.33305602667555e-10</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0001281664881389588</v>
+        <v>1.535170601751901e-10</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0005772557342424989</v>
+        <v>1.069340588299994e-10</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.0001737756392685696</v>
+        <v>1.365329516112013e-10</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0005486300215125084</v>
+        <v>1.179212977264754e-10</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001182194100692868</v>
+        <v>3.891310607073706e-10</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.318472277489491e-05</v>
+        <v>6.693069432017751e-10</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0006109388777986169</v>
+        <v>9.528946520731552e-10</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.001020785188302398</v>
+        <v>1.752931910736777e-09</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.00135058700107038</v>
+        <v>5.630699240199988e-10</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0002780510694719851</v>
+        <v>1.97845781424455e-10</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0008215798297896981</v>
+        <v>1.055394105442531e-09</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.000957043026573956</v>
+        <v>8.885535085489948e-10</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.00157693843357265</v>
+        <v>4.824184107743434e-11</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.001017461414448917</v>
+        <v>3.621766775374624e-11</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0005856992211192846</v>
+        <v>4.595034075460802e-10</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0009563009953126311</v>
+        <v>2.410004695807544e-10</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0001888420665636659</v>
+        <v>7.553796477210994e-11</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0008129468187689781</v>
+        <v>1.310264674536654e-09</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0003865831240545958</v>
+        <v>8.626943603928794e-10</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0001056661858456209</v>
+        <v>6.379989869742531e-10</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0004430781118571758</v>
+        <v>2.503277585219621e-10</v>
       </c>
       <c r="DV4" t="n">
-        <v>8.918580715544522e-05</v>
+        <v>7.280603897541482e-10</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0002543120936024934</v>
+        <v>9.621366897638595e-11</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001837566145695746</v>
+        <v>1.350798917165719e-09</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0002021250402322039</v>
+        <v>7.228098120037885e-10</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0002195728302467614</v>
+        <v>1.002203875444252e-09</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0004511260194703937</v>
+        <v>1.372421842837923e-09</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0002651592076290399</v>
+        <v>3.718814978181939e-10</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0001144485504482873</v>
+        <v>6.70478561559662e-10</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0003258514334447682</v>
+        <v>3.038365392615816e-10</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0003396142274141312</v>
+        <v>5.953797455049425e-10</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0001315532135777175</v>
+        <v>5.317801754500806e-10</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001391921192407608</v>
+        <v>1.084153655739328e-09</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0004016187740489841</v>
+        <v>4.324009761358383e-10</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0001463121006963775</v>
+        <v>2.424097034214867e-10</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0001132878824137151</v>
+        <v>1.761931017751905e-10</v>
       </c>
       <c r="EK4" t="n">
-        <v>2.750684507191181e-05</v>
+        <v>3.631314138274888e-10</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0009223419474437833</v>
+        <v>2.049926201008745e-10</v>
       </c>
       <c r="EM4" t="n">
-        <v>1.481210347265005e-06</v>
+        <v>2.576305835333415e-10</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0002991502988152206</v>
+        <v>8.038165966173239e-11</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0006958770682103932</v>
+        <v>5.09025432915422e-10</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.000234754872508347</v>
+        <v>7.33116067852535e-10</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0009363323915749788</v>
+        <v>4.290530430939299e-11</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0003439134452491999</v>
+        <v>4.236354600450909e-10</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.000470027734991163</v>
+        <v>1.816263112131011e-10</v>
       </c>
       <c r="ET4" t="n">
-        <v>6.792898057028651e-05</v>
+        <v>4.058618163771399e-10</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0005392537568695843</v>
+        <v>6.079165504324635e-10</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0009054298279806972</v>
+        <v>3.079504706793301e-10</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.000336506636813283</v>
+        <v>8.874562196226066e-11</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0004457687609829009</v>
+        <v>2.263891851761457e-10</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001549413660541177</v>
+        <v>3.351977029275588e-10</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0004122919635847211</v>
+        <v>3.045671492785118e-10</v>
       </c>
       <c r="FA4" t="n">
-        <v>4.024158988613635e-05</v>
+        <v>1.491776147055646e-11</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0003570267290342599</v>
+        <v>1.604013311062857e-10</v>
       </c>
       <c r="FC4" t="n">
-        <v>4.740261647384614e-05</v>
+        <v>1.640934749191914e-10</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0006717172218486667</v>
+        <v>1.388686943215589e-10</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0003475784906186163</v>
+        <v>1.107103436703838e-10</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0007096872432157397</v>
+        <v>1.579195246792509e-10</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0002389237779425457</v>
+        <v>5.604613440013395e-10</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0001293317181989551</v>
+        <v>1.041855712813344e-09</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0005803445819765329</v>
+        <v>1.905910984589809e-10</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0002876771613955498</v>
+        <v>1.741205790661837e-10</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0005737886531278491</v>
+        <v>3.627831091090883e-10</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.001433374360203743</v>
+        <v>1.756474132807995e-11</v>
       </c>
       <c r="FM4" t="n">
-        <v>3.991595440311357e-05</v>
+        <v>2.275388211181451e-10</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0009660751093178988</v>
+        <v>8.952156793640142e-10</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.001238832948729396</v>
+        <v>1.20542897885656e-09</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.001017956645227969</v>
+        <v>6.143648922929401e-10</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001610132865607738</v>
+        <v>2.545216259974836e-09</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0008394167525693774</v>
+        <v>2.358256367962497e-10</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0006661817315034568</v>
+        <v>9.556879732031121e-10</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.001038552960380912</v>
+        <v>1.264675253409564e-09</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0007484247325919569</v>
+        <v>9.626910379978426e-10</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0001731903903419152</v>
+        <v>1.283311346078619e-09</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.001264903810806572</v>
+        <v>2.272479093790025e-09</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.001081067835912108</v>
+        <v>6.047123357610928e-10</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.001605139579623938</v>
+        <v>1.807753530203016e-10</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0001108605792978778</v>
+        <v>1.92650895236568e-10</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0008043108973652124</v>
+        <v>9.527874045289764e-10</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0001838179305195808</v>
+        <v>8.55094828278169e-10</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0003180900530423969</v>
+        <v>9.907894504834758e-10</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.001124132191762328</v>
+        <v>6.808524855017595e-10</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.001653045415878296</v>
+        <v>3.766365275215122e-10</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.001669287215918303</v>
+        <v>3.365032696933667e-10</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0003143485228065401</v>
+        <v>2.487991757060826e-10</v>
       </c>
     </row>
     <row r="5">
@@ -3275,1140 +3275,1140 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.008578659035265446</v>
+        <v>0.05204758793115616</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2235151827335358</v>
+        <v>0.2879530191421509</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005905808648094535</v>
+        <v>0.1731271892786026</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1500474959611893</v>
+        <v>0.1883737742900848</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0322083905339241</v>
+        <v>0.0655377209186554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01193795073777437</v>
+        <v>0.06410890072584152</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02600906230509281</v>
+        <v>0.1743164956569672</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04024556279182434</v>
+        <v>0.1518309265375137</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04338635131716728</v>
+        <v>0.1237974092364311</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01311156153678894</v>
+        <v>0.06457459926605225</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1843422204256058</v>
+        <v>0.3688889145851135</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009786143898963928</v>
+        <v>0.1693512052297592</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1353705525398254</v>
+        <v>0.2387472987174988</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06965314596891403</v>
+        <v>0.09049041569232941</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03681443259119987</v>
+        <v>0.0006418321281671524</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01036987081170082</v>
+        <v>0.07339087128639221</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01597492955625057</v>
+        <v>0.2597933709621429</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02353626117110252</v>
+        <v>0.09486982226371765</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01034313905984163</v>
+        <v>0.02796176448464394</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03385379910469055</v>
+        <v>0.0774056538939476</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007555441465228796</v>
+        <v>0.09877923130989075</v>
       </c>
       <c r="V6" t="n">
-        <v>0.006391515024006367</v>
+        <v>0.01027423702180386</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02482645213603973</v>
+        <v>0.01081724278628826</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02858314104378223</v>
+        <v>0.0955108255147934</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02425513416528702</v>
+        <v>0.01002364233136177</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02263618446886539</v>
+        <v>0.0547221377491951</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02730206213891506</v>
+        <v>0.1089172512292862</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02949817478656769</v>
+        <v>0.05292458459734917</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.03371916711330414</v>
+        <v>0.00441471766680479</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.002557233907282352</v>
+        <v>0.03728329390287399</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0003037154674530029</v>
+        <v>0.2473550885915756</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01743646897375584</v>
+        <v>0.05102419480681419</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.03072576224803925</v>
+        <v>0.2075167745351791</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.01435126177966595</v>
+        <v>0.07881928235292435</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.01869674026966095</v>
+        <v>0.01515385136008263</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0008691729744896293</v>
+        <v>0.003758672624826431</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.003768033348023891</v>
+        <v>0.007774154655635357</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.007573921233415604</v>
+        <v>0.2049226313829422</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.003823973704129457</v>
+        <v>0.08343300968408585</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.007096875924617052</v>
+        <v>0.04345522075891495</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.02628292888402939</v>
+        <v>0.1077015101909637</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.01259885355830193</v>
+        <v>0.01473467424511909</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.02000569924712181</v>
+        <v>0.005557198077440262</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.006224758923053741</v>
+        <v>0.05410423502326012</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0002093396615236998</v>
+        <v>0.01187819615006447</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.03636292368173599</v>
+        <v>0.002263870090246201</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.146221324801445</v>
+        <v>0.2716497480869293</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.03243929147720337</v>
+        <v>0.04748820140957832</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.02804071642458439</v>
+        <v>0.1179377138614655</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.002317788545042276</v>
+        <v>0.08181307464838028</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.01959264278411865</v>
+        <v>0.09240617603063583</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.01504190638661385</v>
+        <v>0.00579879991710186</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.03586947172880173</v>
+        <v>0.08680377900600433</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.008715385571122169</v>
+        <v>0.003442457877099514</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.02135693095624447</v>
+        <v>0.03140411898493767</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.04012979194521904</v>
+        <v>0.1918608695268631</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0505296103656292</v>
+        <v>0.1354282796382904</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.04198484122753143</v>
+        <v>0.114291787147522</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.07373012602329254</v>
+        <v>0.1331166326999664</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.006059078499674797</v>
+        <v>0.1174968481063843</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.001676063286140561</v>
+        <v>0.04982014000415802</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.03147873654961586</v>
+        <v>0.1442905515432358</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.009639982134103775</v>
+        <v>0.1891962140798569</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.04203542694449425</v>
+        <v>0.01054083369672298</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0250006765127182</v>
+        <v>0.08595497906208038</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.004576306324452162</v>
+        <v>0.009260467253625393</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.001438185339793563</v>
+        <v>0.06574638187885284</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.03503494709730148</v>
+        <v>0.06154352053999901</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.03196798264980316</v>
+        <v>0.05143210664391518</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.002493998035788536</v>
+        <v>0.03084214590489864</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.03052614443004131</v>
+        <v>0.05539475381374359</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.01096908934414387</v>
+        <v>0.01373947877436876</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.01637525483965874</v>
+        <v>0.03657504543662071</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.06760682910680771</v>
+        <v>0.23887999355793</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.001704863971099257</v>
+        <v>0.03866543993353844</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.01139496266841888</v>
+        <v>0.05457330867648125</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.02798764035105705</v>
+        <v>0.04409829527139664</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.008686572313308716</v>
+        <v>0.08043839782476425</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.01910359598696232</v>
+        <v>0.005335643887519836</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.01018070243299007</v>
+        <v>0.1348490715026855</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.01144565921276808</v>
+        <v>0.0904831662774086</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.009671144187450409</v>
+        <v>0.01645663008093834</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.03628057613968849</v>
+        <v>0.1052024960517883</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.01085347030311823</v>
+        <v>0.04412055760622025</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01578684709966183</v>
+        <v>0.07688851654529572</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.01099778804928064</v>
+        <v>0.01277270261198282</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.003244753926992416</v>
+        <v>0.003615019377321005</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.005585497710853815</v>
+        <v>0.02290617488324642</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0006816466338932514</v>
+        <v>0.02547463588416576</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0110790403559804</v>
+        <v>0.01958014629781246</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.04583197832107544</v>
+        <v>0.07382425665855408</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.01160301268100739</v>
+        <v>0.0523720495402813</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.002749607432633638</v>
+        <v>0.0166473463177681</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.04284165799617767</v>
+        <v>0.2183136641979218</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.02743486315011978</v>
+        <v>0.1468447297811508</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.02485749870538712</v>
+        <v>0.07320763170719147</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0384645015001297</v>
+        <v>0.06525840610265732</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.03598625957965851</v>
+        <v>0.04985865578055382</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0009230673313140869</v>
+        <v>0.1066486984491348</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.008189182728528976</v>
+        <v>0.01332073006778955</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0301639549434185</v>
+        <v>0.1072097420692444</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.01804374158382416</v>
+        <v>0.04237827286124229</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.02415004931390285</v>
+        <v>0.08609938621520996</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0137040251865983</v>
+        <v>0.003602277487516403</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.007356364279985428</v>
+        <v>0.007892133668065071</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.00962124764919281</v>
+        <v>0.02082195319235325</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.005457030609250069</v>
+        <v>0.03146109357476234</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.007940929383039474</v>
+        <v>0.02863841317594051</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.002582724438980222</v>
+        <v>0.0004688911139965057</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.02181300520896912</v>
+        <v>0.0831238254904747</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.03522058203816414</v>
+        <v>0.1531789600849152</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.03821535035967827</v>
+        <v>0.03060578927397728</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0502200573682785</v>
+        <v>0.04519679024815559</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0005719028413295746</v>
+        <v>0.2343987077474594</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.01579077169299126</v>
+        <v>0.05681860446929932</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.02043694816529751</v>
+        <v>0.1672040969133377</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0205993540585041</v>
+        <v>0.02032028511166573</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.003204920329153538</v>
+        <v>0.02728273160755634</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.001021331991069019</v>
+        <v>0.02025222592055798</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.008588102646172047</v>
+        <v>0.01709909364581108</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.01073708198964596</v>
+        <v>0.04265337437391281</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.02664143964648247</v>
+        <v>0.02292190119624138</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.02704992517828941</v>
+        <v>0.002279922366142273</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.00546196848154068</v>
+        <v>0.0224512591958046</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.02333905920386314</v>
+        <v>0.02186884917318821</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.02106661908328533</v>
+        <v>0.1872382760047913</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.000432761269621551</v>
+        <v>0.001944951713085175</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.003576203947886825</v>
+        <v>0.05216258019208908</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0268834475427866</v>
+        <v>0.06238382309675217</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.01997370272874832</v>
+        <v>0.03215415775775909</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01664838939905167</v>
+        <v>0.04954227060079575</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.01173282042145729</v>
+        <v>0.110321931540966</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.01106628309935331</v>
+        <v>0.02749843895435333</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0009457131964154541</v>
+        <v>0.08760595321655273</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.002534389728680253</v>
+        <v>0.0853738859295845</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.003131854347884655</v>
+        <v>0.01915567740797997</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.02990962937474251</v>
+        <v>0.06953363120555878</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.02186927199363708</v>
+        <v>0.02934335172176361</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.01233883574604988</v>
+        <v>0.06803981959819794</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.01901726238429546</v>
+        <v>0.001403640490025282</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.01686590537428856</v>
+        <v>0.05574777722358704</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.007581184152513742</v>
+        <v>0.002224879339337349</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.004792780615389347</v>
+        <v>0.01786903291940689</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.01065674237906933</v>
+        <v>0.01369456760585308</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.00593449454754591</v>
+        <v>0.03743100166320801</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.02493248321115971</v>
+        <v>0.09456361830234528</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.02658180519938469</v>
+        <v>0.0361570417881012</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.004963744897395372</v>
+        <v>0.03443444520235062</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01361383497714996</v>
+        <v>0.08281581103801727</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.00501513946801424</v>
+        <v>0.02497274801135063</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.02180363051593304</v>
+        <v>0.06343624740839005</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.02412628941237926</v>
+        <v>0.0242879930883646</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.01155446097254753</v>
+        <v>0.08590935170650482</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.001663936418481171</v>
+        <v>0.01433790288865566</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.03355708345770836</v>
+        <v>0.1210054531693459</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.008809327147901058</v>
+        <v>0.02598548494279385</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.01904684491455555</v>
+        <v>0.0795707106590271</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.01194653753191233</v>
+        <v>0.001609993632882833</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.009071876294910908</v>
+        <v>0.02331554144620895</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.007900074124336243</v>
+        <v>0.01734304241836071</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.002374876057729125</v>
+        <v>0.0277360025793314</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.01252412330359221</v>
+        <v>0.02554933540523052</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.002439312171190977</v>
+        <v>0.01390480808913708</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.01996315084397793</v>
+        <v>0.05615383014082909</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.02542897500097752</v>
+        <v>0.06575845927000046</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.02253589779138565</v>
+        <v>0.05908334627747536</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.004577752202749252</v>
+        <v>0.07240429520606995</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01502461731433868</v>
+        <v>0.02939658239483833</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0003128829412162304</v>
+        <v>0.0130112748593092</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.003025338985025883</v>
+        <v>0.01717139407992363</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.009784850291907787</v>
+        <v>0.1535246968269348</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.006113780662417412</v>
+        <v>0.03615844249725342</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.02786080352962017</v>
+        <v>0.1118648573756218</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.02817810885608196</v>
+        <v>0.01683720201253891</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.009538163430988789</v>
+        <v>0.04897699132561684</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0008132150396704674</v>
+        <v>0.1274215430021286</v>
       </c>
       <c r="FU6" t="n">
-        <v>3.585312515497208e-05</v>
+        <v>0.01441856101155281</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.008064324036240578</v>
+        <v>0.06497927010059357</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.004379838705062866</v>
+        <v>0.05388687551021576</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.02326301857829094</v>
+        <v>0.0953158512711525</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.0409526452422142</v>
+        <v>0.02603398822247982</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.02219239063560963</v>
+        <v>0.1631811112165451</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.01295960880815983</v>
+        <v>0.08153989166021347</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.01036203652620316</v>
+        <v>0.006105471402406693</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.01558264717459679</v>
+        <v>0.01832802593708038</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.04828029870986938</v>
+        <v>0.01310217473655939</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0704038143157959</v>
+        <v>0.1200007200241089</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.01050527766346931</v>
+        <v>0.03000863082706928</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.02509148977696896</v>
+        <v>0.002427772618830204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.007218755781650543</v>
+        <v>0.2501782178878784</v>
       </c>
       <c r="B7" t="n">
-        <v>0.05461560189723969</v>
+        <v>0.7429022789001465</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004401191603392363</v>
+        <v>0.1588539481163025</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02983341738581657</v>
+        <v>0.0462290421128273</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007744882721453905</v>
+        <v>0.0291440561413765</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03635438531637192</v>
+        <v>0.3559491038322449</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001835808856412768</v>
+        <v>5.352497100830078e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01078577246516943</v>
+        <v>0.06955861300230026</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002907509682700038</v>
+        <v>0.1667465269565582</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01590303145349026</v>
+        <v>0.1062071770429611</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04136510938405991</v>
+        <v>0.9305932521820068</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001151319360360503</v>
+        <v>0.1113831549882889</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02711026556789875</v>
+        <v>0.2255448698997498</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00818951427936554</v>
+        <v>0.1240769699215889</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03853334486484528</v>
+        <v>0.3579082489013672</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001148332376033068</v>
+        <v>0.0658869594335556</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003053740598261356</v>
+        <v>0.1223690956830978</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001919570495374501</v>
+        <v>0.1446337997913361</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00369997788220644</v>
+        <v>0.02061980031430721</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007487220223993063</v>
+        <v>0.2786220014095306</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003298550378531218</v>
+        <v>0.01118011213839054</v>
       </c>
       <c r="V7" t="n">
-        <v>0.005028887651860714</v>
+        <v>0.2187409698963165</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002229802310466766</v>
+        <v>0.08230551332235336</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003590089036151767</v>
+        <v>0.04446346312761307</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.006845231633633375</v>
+        <v>0.03862262144684792</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.004514435306191444</v>
+        <v>0.1702897399663925</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006300732959061861</v>
+        <v>0.01519960723817348</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004200984258204699</v>
+        <v>0.03314623236656189</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.006092866882681847</v>
+        <v>0.1013628765940666</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.002311261836439371</v>
+        <v>0.08244166523218155</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0001898912014439702</v>
+        <v>0.2763365507125854</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.002140944357961416</v>
+        <v>0.4544695317745209</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00123286375310272</v>
+        <v>0.1358060389757156</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.003879040945321321</v>
+        <v>0.06445352733135223</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.002936735982075334</v>
+        <v>0.1931433528661728</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001291328808292747</v>
+        <v>0.02505125664174557</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.004662847146391869</v>
+        <v>0.03243212401866913</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.00804592203348875</v>
+        <v>0.3284488320350647</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.003007578197866678</v>
+        <v>0.04421632364392281</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.002082114573568106</v>
+        <v>0.07914736866950989</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.002400475786998868</v>
+        <v>0.1641485840082169</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.006996718235313892</v>
+        <v>0.1476525515317917</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001401613350026309</v>
+        <v>0.1099929511547089</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.002931518945842981</v>
+        <v>0.203693151473999</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.007391604594886303</v>
+        <v>0.09070750325918198</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.004580902867019176</v>
+        <v>0.09904784709215164</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.03525631874799728</v>
+        <v>0.901274561882019</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.00321524147875607</v>
+        <v>0.06261792778968811</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.001091940677724779</v>
+        <v>0.03194588795304298</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0004544354742392898</v>
+        <v>0.1305863708257675</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0201130099594593</v>
+        <v>0.4377061724662781</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.000342424726113677</v>
+        <v>0.004089284688234329</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.01126221753656864</v>
+        <v>0.005805551074445248</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0115499421954155</v>
+        <v>0.05478841066360474</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.009033763781189919</v>
+        <v>0.1079650148749352</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.009994049556553364</v>
+        <v>0.2502525746822357</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.01481299195438623</v>
+        <v>0.04870309680700302</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.009418386034667492</v>
+        <v>0.1651071161031723</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01680595800280571</v>
+        <v>0.2831132709980011</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.010627631098032</v>
+        <v>0.02051274105906487</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.003358031855896115</v>
+        <v>0.09361225366592407</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.01315542962402105</v>
+        <v>0.09852428734302521</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0008801198564469814</v>
+        <v>0.1492645740509033</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.00136219582054764</v>
+        <v>0.09723950177431107</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.008215834386646748</v>
+        <v>0.03419334068894386</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.006666149944067001</v>
+        <v>0.03882088512182236</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.008240084163844585</v>
+        <v>0.04967548325657845</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0006994567811489105</v>
+        <v>0.01588080823421478</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0001765235210768878</v>
+        <v>0.1078061163425446</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.007033509202301502</v>
+        <v>0.1049191206693649</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.001446625916287303</v>
+        <v>0.08255936205387115</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0003867013147100806</v>
+        <v>0.1106901094317436</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.003000614698976278</v>
+        <v>0.09370626509189606</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.01763598062098026</v>
+        <v>0.6452550292015076</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.008367924951016903</v>
+        <v>0.02153582870960236</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.005882951430976391</v>
+        <v>0.104934997856617</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.004799181595444679</v>
+        <v>0.008773691952228546</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.006247558631002903</v>
+        <v>0.2573769092559814</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.005662478506565094</v>
+        <v>0.07995852828025818</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.005225323140621185</v>
+        <v>0.0663229376077652</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.008421776816248894</v>
+        <v>0.02789349853992462</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0003676622873172164</v>
+        <v>0.01458596810698509</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.008879200555384159</v>
+        <v>0.259774386882782</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.007271755952388048</v>
+        <v>0.0359211377799511</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.005336781963706017</v>
+        <v>0.03985671326518059</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.003838079748675227</v>
+        <v>0.01513584144413471</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.006465128622949123</v>
+        <v>0.1107710748910904</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.003169306088238955</v>
+        <v>0.0589636005461216</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.001688639749772847</v>
+        <v>0.04355130344629288</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.004901373758912086</v>
+        <v>0.01847649738192558</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.007015210576355457</v>
+        <v>0.2545660734176636</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.001081138965673745</v>
+        <v>0.3877437114715576</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.003305792342871428</v>
+        <v>0.03653875738382339</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.006357442121952772</v>
+        <v>0.3531376123428345</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.001222084509208798</v>
+        <v>0.3651606440544128</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0001456254394724965</v>
+        <v>0.2808529138565063</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.00606158934533596</v>
+        <v>0.05669425427913666</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.005938970483839512</v>
+        <v>0.01644542440772057</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0003328912134747952</v>
+        <v>0.07220207154750824</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0005114569212310016</v>
+        <v>0.05068213120102882</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.007957130670547485</v>
+        <v>0.2428334504365921</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.006999832578003407</v>
+        <v>0.03220362216234207</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.007952043786644936</v>
+        <v>0.04680666700005531</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.003531452734023333</v>
+        <v>0.01903021708130836</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.00703863613307476</v>
+        <v>0.1156101375818253</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.003062532050535083</v>
+        <v>0.02122087962925434</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.004940298851579428</v>
+        <v>0.07389762252569199</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.003364247037097812</v>
+        <v>0.004461543168872595</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001462456770241261</v>
+        <v>0.06499671190977097</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.01026070769876242</v>
+        <v>0.0217379555106163</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.001987850526347756</v>
+        <v>0.0574810691177845</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01974758878350258</v>
+        <v>0.01021549478173256</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.003685611300170422</v>
+        <v>0.3155572116374969</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.003176820231601596</v>
+        <v>0.164416715502739</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.008199616335332394</v>
+        <v>0.1077235043048859</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.008430884219706059</v>
+        <v>0.1138313487172127</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.002997552510350943</v>
+        <v>0.03059538081288338</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0004863738140556961</v>
+        <v>0.01379574276506901</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.00171412224881351</v>
+        <v>0.1155722439289093</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.004393508657813072</v>
+        <v>0.01240359246730804</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.00431794673204422</v>
+        <v>0.1324938535690308</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.003621190320700407</v>
+        <v>0.02900428883731365</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0005842770333401859</v>
+        <v>0.004376303404569626</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.00249043689109385</v>
+        <v>0.01727888733148575</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0004490301362238824</v>
+        <v>0.1760598421096802</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.007487136404961348</v>
+        <v>0.03662662953138351</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0017088569002226</v>
+        <v>0.1053315550088882</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.004011516459286213</v>
+        <v>0.08058153092861176</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.008920732885599136</v>
+        <v>0.1072593182325363</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.646772190928459e-05</v>
+        <v>0.01675727590918541</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.002699265955016017</v>
+        <v>0.06576603651046753</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.003958108834922314</v>
+        <v>0.1177182495594025</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.000567487848456949</v>
+        <v>0.04030049592256546</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.002996620023623109</v>
+        <v>0.04764656722545624</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.000716358597856015</v>
+        <v>0.04204403981566429</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.003759102430194616</v>
+        <v>0.0131743811070919</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.005547748412936926</v>
+        <v>0.07729953527450562</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.005228772759437561</v>
+        <v>0.02523037046194077</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.001059953472577035</v>
+        <v>0.03620463237166405</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.001074762432835996</v>
+        <v>0.0349632240831852</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.005157124251127243</v>
+        <v>0.05162008851766586</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.005802891682833433</v>
+        <v>0.02217577025294304</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0003692242607939988</v>
+        <v>0.007330050691962242</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.001258969423361123</v>
+        <v>0.009026659652590752</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.001527480082586408</v>
+        <v>0.04300757497549057</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.003339594230055809</v>
+        <v>0.1018495410680771</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.007612292189151049</v>
+        <v>0.02443584613502026</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.005116850137710571</v>
+        <v>0.02841841988265514</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.005368432495743036</v>
+        <v>0.09954416751861572</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.007105207536369562</v>
+        <v>0.03680077195167542</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.006582652218639851</v>
+        <v>0.01383248716592789</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.008581720292568207</v>
+        <v>0.07315991818904877</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0002583012101240456</v>
+        <v>0.03564231470227242</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0008334147278219461</v>
+        <v>0.00914333388209343</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.007494660560041666</v>
+        <v>0.2668460607528687</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.005510799586772919</v>
+        <v>0.03073722124099731</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.006478347815573215</v>
+        <v>0.05444527044892311</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.004320628941059113</v>
+        <v>0.01418538484722376</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.005572123453021049</v>
+        <v>0.1088945418596268</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.00529217766597867</v>
+        <v>0.07782591879367828</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.002675909083336592</v>
+        <v>0.06570596992969513</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.005557161755859852</v>
+        <v>0.01528078317642212</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0008779282215982676</v>
+        <v>0.06432383507490158</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.004072945564985275</v>
+        <v>0.2426932454109192</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.006841674447059631</v>
+        <v>0.005094664171338081</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.007774768862873316</v>
+        <v>0.2087477594614029</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.00278412620536983</v>
+        <v>0.1081410422921181</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.004519511479884386</v>
+        <v>0.1823590099811554</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.003232197836041451</v>
+        <v>0.1245376840233803</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.002293246332556009</v>
+        <v>0.2234414368867874</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.003861743956804276</v>
+        <v>0.0118524432182312</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.002447091042995453</v>
+        <v>0.04162345454096794</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.009151868522167206</v>
+        <v>0.4686972200870514</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.004689530469477177</v>
+        <v>0.02441682107746601</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0110440868884325</v>
+        <v>0.2536850571632385</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.009517543949186802</v>
+        <v>0.04438292607665062</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.004299065098166466</v>
+        <v>0.1379425525665283</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.003908136859536171</v>
+        <v>0.07445166260004044</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.004093077965080738</v>
+        <v>0.03448044136166573</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.001285971608012915</v>
+        <v>0.06889426708221436</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0105725210160017</v>
+        <v>0.05271521955728531</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0003718350199051201</v>
+        <v>0.1771637201309204</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.001614247681573033</v>
+        <v>0.002446535974740982</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0005998066626489162</v>
+        <v>0.08251215517520905</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.002987996209412813</v>
+        <v>0.001166656613349915</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.005028645507991314</v>
+        <v>0.01101135648787022</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.02557180821895599</v>
+        <v>0.1077786684036255</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.001850734348408878</v>
+        <v>0.1452810913324356</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.003592755878344178</v>
+        <v>0.1341572701931</v>
       </c>
     </row>
     <row r="8">
@@ -4982,2278 +4982,2278 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.4218282699584961</v>
+        <v>0.001005750382319093</v>
       </c>
       <c r="B9" t="n">
-        <v>1.097612857818604</v>
+        <v>0.002903488231822848</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1600079238414764</v>
+        <v>2.634123666211963e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1131145060062408</v>
+        <v>0.0001700492575764656</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2645275294780731</v>
+        <v>0.0009216636535711586</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1831982135772705</v>
+        <v>0.003634068183600903</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01235455274581909</v>
+        <v>0.002341780113056302</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6468414664268494</v>
+        <v>0.0008048216695897281</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09353452920913696</v>
+        <v>0.0007032792782410979</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3090660274028778</v>
+        <v>0.003787737805396318</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9580173492431641</v>
+        <v>0.002723719226196408</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09183251112699509</v>
+        <v>0.0008602276211604476</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009680449962615967</v>
+        <v>0.00288557936437428</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1686122715473175</v>
+        <v>0.004287183750420809</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1918127685785294</v>
+        <v>0.003631926374509931</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01930278539657593</v>
+        <v>0.005542629398405552</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8240554928779602</v>
+        <v>0.003286894643679261</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3568995296955109</v>
+        <v>0.00163269869517535</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1513089388608932</v>
+        <v>0.002490377752110362</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06259334087371826</v>
+        <v>0.00400796951726079</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05914756655693054</v>
+        <v>0.0009398979600518942</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2263971567153931</v>
+        <v>0.002610686700791121</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02615055255591869</v>
+        <v>0.001876568770967424</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1327045261859894</v>
+        <v>0.001453546108677983</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09035459160804749</v>
+        <v>0.0008235436980612576</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2093869745731354</v>
+        <v>0.002363678766414523</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03793538734316826</v>
+        <v>0.001268775318749249</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.09831631928682327</v>
+        <v>7.097446359694004e-05</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.205690786242485</v>
+        <v>0.0008504178840667009</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2030943334102631</v>
+        <v>0.0008582226000726223</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.008347038179636002</v>
+        <v>0.00401717983186245</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.202234223484993</v>
+        <v>0.002913468517363071</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.02513659372925758</v>
+        <v>0.0009259998914785683</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1010961830615997</v>
+        <v>0.0002622687024995685</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.1918756514787674</v>
+        <v>0.001889527426101267</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0007533431053161621</v>
+        <v>0.0003317749651614577</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.3919606804847717</v>
+        <v>0.003250125795602798</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.06326981633901596</v>
+        <v>0.003358399728313088</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.07321920990943909</v>
+        <v>0.0001856229355325922</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0460294783115387</v>
+        <v>0.001901417970657349</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.1866647154092789</v>
+        <v>0.001158466096967459</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.006123547907918692</v>
+        <v>0.0007969724829308689</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.09886832535266876</v>
+        <v>4.161658580414951e-05</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01706821098923683</v>
+        <v>4.111573070986196e-05</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.1013741791248322</v>
+        <v>5.566849722526968e-05</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.05900658667087555</v>
+        <v>0.00485271355137229</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.18938410282135</v>
+        <v>0.006765695288777351</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.05269061028957367</v>
+        <v>0.00119293259922415</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.1195570826530457</v>
+        <v>0.001130279270000756</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1783644407987595</v>
+        <v>0.0002516030799597502</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.1121475175023079</v>
+        <v>0.00123409868683666</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.05327417701482773</v>
+        <v>0.0009942289907485247</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.03004528768360615</v>
+        <v>0.001027681631967425</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.09304144233465195</v>
+        <v>0.001960687339305878</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.1875386536121368</v>
+        <v>0.002535493345931172</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.3914834260940552</v>
+        <v>0.003507251152768731</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.4203449189662933</v>
+        <v>0.0005889991880394518</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.3196893930435181</v>
+        <v>0.0004911355208605528</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.2924729287624359</v>
+        <v>0.007095852866768837</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.06838728487491608</v>
+        <v>0.0003689210570883006</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.2336067706346512</v>
+        <v>0.002918056910857558</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.3763871192932129</v>
+        <v>0.0002600960433483124</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.01928908564150333</v>
+        <v>0.0001096096821129322</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.1182264983654022</v>
+        <v>2.381148806307465e-05</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.881822407245636</v>
+        <v>0.001287240767851472</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0634811744093895</v>
+        <v>0.0005411884048953652</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.4590972065925598</v>
+        <v>0.0009570273687131703</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.6704460382461548</v>
+        <v>0.00230754422955215</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.09304090589284897</v>
+        <v>0.003538314718753099</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.1860586404800415</v>
+        <v>0.0004254676459822804</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.3117288053035736</v>
+        <v>0.0005306750535964966</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.01159706525504589</v>
+        <v>1.215804513776675e-05</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.01806224882602692</v>
+        <v>0.005432240199297667</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.5731280446052551</v>
+        <v>0.006185538601130247</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.2185289710760117</v>
+        <v>0.0008662806358188391</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.08393403887748718</v>
+        <v>0.002182127442210913</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.2122927606105804</v>
+        <v>0.0003657512133941054</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.1507429629564285</v>
+        <v>0.001049598795361817</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.3061491250991821</v>
+        <v>0.001309307641349733</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.01962251588702202</v>
+        <v>0.002039380604401231</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.05008070915937424</v>
+        <v>0.000451353145763278</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.006699668243527412</v>
+        <v>0.0008937082020565867</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.1904750764369965</v>
+        <v>0.0009419888374395669</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.09336689114570618</v>
+        <v>0.0004192983324173838</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01821444928646088</v>
+        <v>0.001195627846755087</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0757630467414856</v>
+        <v>0.000421443983213976</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.1450636833906174</v>
+        <v>0.001392999081872404</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.003286534920334816</v>
+        <v>0.0006784413708373904</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.1381560564041138</v>
+        <v>0.0002495474764145911</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.102035328745842</v>
+        <v>0.0004790417442563921</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.5548542141914368</v>
+        <v>0.001693401602096856</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.8153091073036194</v>
+        <v>0.002998654730618</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.08216622471809387</v>
+        <v>0.0008811418665573001</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.3660366237163544</v>
+        <v>0.00069046625867486</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.5465689897537231</v>
+        <v>0.006432445719838142</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.09869691729545593</v>
+        <v>2.465737452439498e-05</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.03476992249488831</v>
+        <v>0.003023522906005383</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.1829895228147507</v>
+        <v>0.001765392138622701</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.08140429109334946</v>
+        <v>0.001639570924453437</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0248570404946804</v>
+        <v>0.0004771624226123095</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.1442253738641739</v>
+        <v>0.000593055912759155</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.1206112056970596</v>
+        <v>0.0006298826192505658</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.09274818748235703</v>
+        <v>0.001344215823337436</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.04503149539232254</v>
+        <v>0.0003934840206056833</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.1241963282227516</v>
+        <v>0.001189271686598659</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.01485391706228256</v>
+        <v>0.0006898126448504627</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.04204763472080231</v>
+        <v>0.0009328813757747412</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.06810405850410461</v>
+        <v>0.0004958424251526594</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.5295017957687378</v>
+        <v>0.0003508361987769604</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.2534143328666687</v>
+        <v>0.0005282287602312863</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0569302886724472</v>
+        <v>8.151240763254464e-05</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.8010786175727844</v>
+        <v>0.002649092581123114</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03323888033628464</v>
+        <v>0.002469668164849281</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.05292979627847672</v>
+        <v>0.001300442032516003</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.5615151524543762</v>
+        <v>0.00071860256139189</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.1316789388656616</v>
+        <v>0.002215102082118392</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.03681455552577972</v>
+        <v>0.006600026972591877</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.2210229486227036</v>
+        <v>0.00263502961024642</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.2948979437351227</v>
+        <v>0.001037076232023537</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.1193618327379227</v>
+        <v>1.104266266338527e-05</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.2580579221248627</v>
+        <v>0.00181520963087678</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0075570666231215</v>
+        <v>0.0001997277286136523</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.02320260182023048</v>
+        <v>0.003860672237351537</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.05404692888259888</v>
+        <v>0.0003565082151908427</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.2586784064769745</v>
+        <v>0.001862268894910812</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.03308502584695816</v>
+        <v>2.858225343516096e-05</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.1137929335236549</v>
+        <v>0.0003402784059289843</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.182535782456398</v>
+        <v>0.0007584228296764195</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.1031900644302368</v>
+        <v>0.0001250919740414247</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.2331858575344086</v>
+        <v>0.001665739924646914</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.003971700556576252</v>
+        <v>0.003668936900794506</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.2722679972648621</v>
+        <v>0.0004512122832238674</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.2432682663202286</v>
+        <v>0.001981757814064622</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.08900748193264008</v>
+        <v>0.001323070377111435</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0500255674123764</v>
+        <v>0.0001176460646092892</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.08144775032997131</v>
+        <v>0.0001139953965321183</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.08629029989242554</v>
+        <v>0.0003142192726954818</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.02912984788417816</v>
+        <v>0.0011687126243487</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.2715325951576233</v>
+        <v>0.001126942224800587</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.009365865029394627</v>
+        <v>0.001135314931161702</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.06605345755815506</v>
+        <v>0.0009650591528043151</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.01431284099817276</v>
+        <v>0.00171447591856122</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.1047897189855576</v>
+        <v>0.0004501685034483671</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.1085756495594978</v>
+        <v>0.0008033870835788548</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.2155562490224838</v>
+        <v>0.0006375873927026987</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.04546145722270012</v>
+        <v>0.001148011069744825</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.1181753873825073</v>
+        <v>0.0008481447002850473</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.01438345387578011</v>
+        <v>0.0006903192261233926</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.06224359571933746</v>
+        <v>0.001206292305141687</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.1501217037439346</v>
+        <v>0.0009664057288318872</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.1624824702739716</v>
+        <v>0.001437737722881138</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.2604555785655975</v>
+        <v>0.00117676449008286</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.05775105208158493</v>
+        <v>0.001355171669274569</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.008257470093667507</v>
+        <v>0.001034610089845955</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.1290307641029358</v>
+        <v>0.0005649717641063035</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.05567165464162827</v>
+        <v>0.0006067997892387211</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.04049121588468552</v>
+        <v>0.001419693580828607</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.02597673423588276</v>
+        <v>0.0002577635459601879</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.132136270403862</v>
+        <v>0.001009525964036584</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.06347159296274185</v>
+        <v>0.00081790512194857</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.1554137170314789</v>
+        <v>0.001143726753070951</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.09933213889598846</v>
+        <v>0.00110442063305527</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.08356215059757233</v>
+        <v>0.0005958686815574765</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.01475138124078512</v>
+        <v>0.000844586465973407</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.1054864749312401</v>
+        <v>0.001738416031002998</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.01828937977552414</v>
+        <v>0.002668284345418215</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.1143063604831696</v>
+        <v>5.816081829834729e-05</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.09124609082937241</v>
+        <v>5.286735540721565e-05</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.08093750476837158</v>
+        <v>0.0004280568682588637</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.1479528248310089</v>
+        <v>0.0001173662603832781</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.05675181001424789</v>
+        <v>0.002002542605623603</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.2244195938110352</v>
+        <v>0.001534680603072047</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0427982434630394</v>
+        <v>0.005270448047667742</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.208825409412384</v>
+        <v>0.005770764779299498</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.3816444873809814</v>
+        <v>0.0022422862239182</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.04525452479720116</v>
+        <v>0.001096502877771854</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.01196152344346046</v>
+        <v>0.0009474286343902349</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.01554960012435913</v>
+        <v>4.647756577469409e-05</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.006833152379840612</v>
+        <v>0.0004703124286606908</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.06260483711957932</v>
+        <v>0.002563764108344913</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.2658186554908752</v>
+        <v>0.002261323155835271</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.3045995831489563</v>
+        <v>0.002833998762071133</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.1799472272396088</v>
+        <v>0.001470641465857625</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.01755852997303009</v>
+        <v>0.003444134490564466</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.4062556624412537</v>
+        <v>0.002453465946018696</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.1177887097001076</v>
+        <v>7.623282726854086e-05</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.3994768261909485</v>
+        <v>0.0004084666143171489</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.07124529033899307</v>
+        <v>0.0005498154787346721</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.03013594262301922</v>
+        <v>0.0005158133571967483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.2531976699829102</v>
+        <v>0.6387443542480469</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5225329995155334</v>
+        <v>2.211943387985229</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02087605744600296</v>
+        <v>0.5376169681549072</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1902709007263184</v>
+        <v>0.6231043338775635</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2488253265619278</v>
+        <v>0.5588555335998535</v>
       </c>
       <c r="F10" t="n">
-        <v>0.176786944270134</v>
+        <v>0.3266230225563049</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1145397201180458</v>
+        <v>0.3579997718334198</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1299138367176056</v>
+        <v>0.3208160996437073</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1072655096650124</v>
+        <v>0.3044522404670715</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1870312094688416</v>
+        <v>0.377765417098999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3613005876541138</v>
+        <v>3.003515720367432</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04891610145568848</v>
+        <v>0.8262894749641418</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03475118800997734</v>
+        <v>0.922249972820282</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5590652227401733</v>
+        <v>0.686005175113678</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2778925895690918</v>
+        <v>0.1419350057840347</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02769016847014427</v>
+        <v>0.02204342186450958</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4955963492393494</v>
+        <v>0.344507098197937</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1505354046821594</v>
+        <v>0.4521916806697845</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01104496512562037</v>
+        <v>0.1214039325714111</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2726786732673645</v>
+        <v>0.1137028187513351</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07692574709653854</v>
+        <v>0.09553477168083191</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01848968863487244</v>
+        <v>0.3136619925498962</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2364818155765533</v>
+        <v>0.1155972331762314</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1553293317556381</v>
+        <v>0.06318307667970657</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.04448634758591652</v>
+        <v>0.0713387131690979</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.05182148143649101</v>
+        <v>0.1294632256031036</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.06586474180221558</v>
+        <v>0.4107368588447571</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.00937681645154953</v>
+        <v>0.06498450040817261</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1797077357769012</v>
+        <v>0.2765949070453644</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.04781407117843628</v>
+        <v>0.2129034996032715</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.2450134754180908</v>
+        <v>0.1860086619853973</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.09580587595701218</v>
+        <v>0.376581072807312</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.2294134795665741</v>
+        <v>0.485493540763855</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.1581279188394547</v>
+        <v>0.1232352256774902</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.1641907244920731</v>
+        <v>0.5309041738510132</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.02513372153043747</v>
+        <v>0.2052585184574127</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.1741741448640823</v>
+        <v>0.08679401874542236</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1785591840744019</v>
+        <v>0.4753530621528625</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.04316899925470352</v>
+        <v>0.224835529923439</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.06260865181684494</v>
+        <v>0.3075175881385803</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.05264902114868164</v>
+        <v>0.3523014783859253</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.1673028916120529</v>
+        <v>0.04642093554139137</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.1739823818206787</v>
+        <v>0.1651302129030228</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.2077557444572449</v>
+        <v>0.3034013211727142</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.07790264487266541</v>
+        <v>0.02905284240841866</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.2872639000415802</v>
+        <v>0.1936143040657043</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6381533741950989</v>
+        <v>2.034307956695557</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.03532929718494415</v>
+        <v>0.151071310043335</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2851249575614929</v>
+        <v>0.4155682325363159</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.4240001142024994</v>
+        <v>0.5279831290245056</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.03832605481147766</v>
+        <v>0.1426305323839188</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1000292077660561</v>
+        <v>0.02434814535081387</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.1728321462869644</v>
+        <v>0.163719043135643</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.09856030344963074</v>
+        <v>0.06274334341287613</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.1866379082202911</v>
+        <v>0.4388968348503113</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.1014700084924698</v>
+        <v>0.09138017892837524</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.04741883277893066</v>
+        <v>0.4006399512290955</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.06222524493932724</v>
+        <v>0.1697437614202499</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.4409392774105072</v>
+        <v>0.09832172840833664</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.09091999381780624</v>
+        <v>0.1424178183078766</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.04407409206032753</v>
+        <v>0.0215647928416729</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.359322190284729</v>
+        <v>0.2558334767818451</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.128979280591011</v>
+        <v>0.08446343243122101</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.02628928422927856</v>
+        <v>0.04612765461206436</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.2622984051704407</v>
+        <v>0.6784181594848633</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.02396234311163425</v>
+        <v>0.2042380571365356</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.3817032873630524</v>
+        <v>0.04985766112804413</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.6086454391479492</v>
+        <v>0.4550421833992004</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.1382081359624863</v>
+        <v>0.08424998074769974</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.004819426685571671</v>
+        <v>0.6496819853782654</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.30667445063591</v>
+        <v>0.1812846213579178</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.1688543111085892</v>
+        <v>0.08917444199323654</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.1605170220136642</v>
+        <v>0.1723829209804535</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.3291171789169312</v>
+        <v>1.256980538368225</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.04490192979574203</v>
+        <v>0.03818319737911224</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.04136669635772705</v>
+        <v>0.4070393443107605</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.1365652531385422</v>
+        <v>0.1046892255544662</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.03091741167008877</v>
+        <v>0.07874280214309692</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.2295096963644028</v>
+        <v>0.3242822587490082</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.1512453258037567</v>
+        <v>0.03168286755681038</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.04659466445446014</v>
+        <v>0.3183348178863525</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.04820456355810165</v>
+        <v>0.09713450819253922</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.1008763015270233</v>
+        <v>0.7013368606567383</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0248030349612236</v>
+        <v>0.1689022928476334</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.04247215390205383</v>
+        <v>0.03702907636761665</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.004791555926203728</v>
+        <v>0.07338224351406097</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.01388816256076097</v>
+        <v>0.2575143277645111</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.01429008692502975</v>
+        <v>0.07658996433019638</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.01962229609489441</v>
+        <v>0.1110727488994598</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.01207123044878244</v>
+        <v>0.08412481844425201</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.2879827916622162</v>
+        <v>0.3245396316051483</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.1710752993822098</v>
+        <v>1.48613715171814</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.02691248431801796</v>
+        <v>0.1603742837905884</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.04705210402607918</v>
+        <v>0.1938348412513733</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.5287172198295593</v>
+        <v>0.4161723554134369</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.01646113954484463</v>
+        <v>0.3560973405838013</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.08224408328533173</v>
+        <v>0.1058718040585518</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.02706635370850563</v>
+        <v>0.09651648253202438</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0866742730140686</v>
+        <v>0.02644307538866997</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.004781824536621571</v>
+        <v>0.03074585646390915</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1014780402183533</v>
+        <v>0.7274938821792603</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.02273755334317684</v>
+        <v>0.1752332895994186</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.08647753298282623</v>
+        <v>0.1349730342626572</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.02498870342969894</v>
+        <v>0.05980108678340912</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.05139937996864319</v>
+        <v>0.2482889741659164</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.01419047452509403</v>
+        <v>0.04124553501605988</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.03756820783019066</v>
+        <v>0.08005113154649734</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.01313352677971125</v>
+        <v>0.1608391106128693</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.3607133626937866</v>
+        <v>0.2070474475622177</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.700391411781311</v>
+        <v>0.9520881175994873</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.04909985512495041</v>
+        <v>0.03210318833589554</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.04606420919299126</v>
+        <v>0.4940654337406158</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.04134544730186462</v>
+        <v>0.09042768180370331</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.3191681504249573</v>
+        <v>1.027463436126709</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.2573825418949127</v>
+        <v>0.04321293160319328</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2013511955738068</v>
+        <v>0.2576998174190521</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.1614691466093063</v>
+        <v>0.2769433259963989</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.2133015841245651</v>
+        <v>0.09483614563941956</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.1799994707107544</v>
+        <v>0.4306357502937317</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.05341169983148575</v>
+        <v>0.268405944108963</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.1109808161854744</v>
+        <v>0.1666650176048279</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.09909531474113464</v>
+        <v>0.1135646104812622</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.02352847345173359</v>
+        <v>0.01989679411053658</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1603705286979675</v>
+        <v>0.1890224814414978</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.07845384627580643</v>
+        <v>0.4293272197246552</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.1274354159832001</v>
+        <v>0.2311910390853882</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.07850871980190277</v>
+        <v>0.4848321974277496</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.07921967655420303</v>
+        <v>0.3533934950828552</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.123454712331295</v>
+        <v>0.0799155980348587</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.2397498935461044</v>
+        <v>0.1988241076469421</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0728190541267395</v>
+        <v>0.0785248801112175</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.07023161649703979</v>
+        <v>0.4077824056148529</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.07502157241106033</v>
+        <v>0.0210961252450943</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.07637220621109009</v>
+        <v>0.5741178393363953</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.09288766980171204</v>
+        <v>0.3817334473133087</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.1066064983606339</v>
+        <v>0.03025852143764496</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.1915081292390823</v>
+        <v>0.4016779363155365</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.03059831261634827</v>
+        <v>0.05263277888298035</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0931817814707756</v>
+        <v>0.1141088902950287</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01354052871465683</v>
+        <v>0.1110531538724899</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.069024458527565</v>
+        <v>0.316908985376358</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.06361977756023407</v>
+        <v>0.03725635632872581</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.03679761663079262</v>
+        <v>0.1355271190404892</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0406714491546154</v>
+        <v>0.09792985767126083</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0722876638174057</v>
+        <v>0.2732174396514893</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.007606941275298595</v>
+        <v>0.3278295397758484</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01631161756813526</v>
+        <v>0.0770663395524025</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.07715974003076553</v>
+        <v>0.06772145628929138</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01026155985891819</v>
+        <v>0.1095634922385216</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06415116041898727</v>
+        <v>0.1618278026580811</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.03644607216119766</v>
+        <v>0.1247515305876732</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.061737310141325</v>
+        <v>0.1340311914682388</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.05785547196865082</v>
+        <v>0.1743773221969604</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.05123250186443329</v>
+        <v>0.05299658328294754</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.07159793376922607</v>
+        <v>0.8657369613647461</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0115388473495841</v>
+        <v>0.1450140178203583</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.06201992556452751</v>
+        <v>0.08028583228588104</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01171673648059368</v>
+        <v>0.08432783931493759</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.02910018339753151</v>
+        <v>0.2725906074047089</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.003110745921730995</v>
+        <v>0.09957695752382278</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.05312306806445122</v>
+        <v>0.01108228787779808</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.009216884151101112</v>
+        <v>0.1975536495447159</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.219691663980484</v>
+        <v>0.1026828587055206</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.1312863826751709</v>
+        <v>0.1916609108448029</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.05618064478039742</v>
+        <v>0.2188035845756531</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.08649105578660965</v>
+        <v>0.1105911731719971</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.03469787910580635</v>
+        <v>0.2631993293762207</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.002686877734959126</v>
+        <v>0.05442842096090317</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.04875565692782402</v>
+        <v>0.1351401507854462</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.09365539252758026</v>
+        <v>0.01937512680888176</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.04305960610508919</v>
+        <v>0.01733842492103577</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.07759817689657211</v>
+        <v>0.1192256584763527</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.02845668978989124</v>
+        <v>0.1006149798631668</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.08695807307958603</v>
+        <v>0.606014609336853</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.5164594650268555</v>
+        <v>0.3426015079021454</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.2426977902650833</v>
+        <v>0.7301771640777588</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001452707219868898</v>
+        <v>0.2544496953487396</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.02997744083404541</v>
+        <v>0.1323802024126053</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.05050607025623322</v>
+        <v>0.02304151654243469</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.09510645270347595</v>
+        <v>0.5377449989318848</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.02837840467691422</v>
+        <v>0.01232193037867546</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.2363066226243973</v>
+        <v>0.4086261093616486</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.07831232249736786</v>
+        <v>0.1780615895986557</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4308517873287201</v>
+        <v>0.01663294434547424</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.3809125423431396</v>
+        <v>0.1749583929777145</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.1533296257257462</v>
+        <v>0.2914915978908539</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.2681801319122314</v>
+        <v>0.3683438003063202</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.355555921792984</v>
+        <v>0.298391580581665</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.03675857931375504</v>
+        <v>0.2586278319358826</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.01442908402532339</v>
+        <v>0.07122930884361267</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3079389333724976</v>
+        <v>0.3001164793968201</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02018347941339016</v>
+        <v>0.1087353676557541</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1405993551015854</v>
+        <v>0.04986938461661339</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09758090227842331</v>
+        <v>0.1750341206789017</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07808669656515121</v>
+        <v>0.2976590991020203</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1340034157037735</v>
+        <v>0.2391604036092758</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003178100101649761</v>
+        <v>0.02707682922482491</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01393621228635311</v>
+        <v>0.1503280699253082</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03044232167303562</v>
+        <v>0.07236163318157196</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2254224866628647</v>
+        <v>0.438528835773468</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007536315824836493</v>
+        <v>0.0315268263220787</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1944984346628189</v>
+        <v>0.06245686858892441</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1036641597747803</v>
+        <v>0.1982257962226868</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1002077013254166</v>
+        <v>0.1681087762117386</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1210476905107498</v>
+        <v>0.3170868754386902</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03376849740743637</v>
+        <v>0.03398874402046204</v>
       </c>
       <c r="R11" t="n">
-        <v>0.02519850619137287</v>
+        <v>0.05356340110301971</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04186031967401505</v>
+        <v>0.02421765029430389</v>
       </c>
       <c r="T11" t="n">
-        <v>0.06656886637210846</v>
+        <v>0.04751769453287125</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01799267157912254</v>
+        <v>0.004213830456137657</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001000214368104935</v>
+        <v>0.03935546055436134</v>
       </c>
       <c r="W11" t="n">
-        <v>0.06046577915549278</v>
+        <v>0.07136288285255432</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03895457088947296</v>
+        <v>0.06693800538778305</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.003589281346648932</v>
+        <v>0.08064523339271545</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.008133817464113235</v>
+        <v>0.01067488547414541</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02997900359332561</v>
+        <v>0.004955823067575693</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02247823774814606</v>
+        <v>0.002876438200473785</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.05785432085394859</v>
+        <v>0.05465701222419739</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.008978519588708878</v>
+        <v>0.180050790309906</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.009634747169911861</v>
+        <v>0.06567397713661194</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0149706294760108</v>
+        <v>0.09536934643983841</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01857009530067444</v>
+        <v>0.01197184063494205</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.00637890538200736</v>
+        <v>0.002799534238874912</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.00384812243282795</v>
+        <v>0.1137724071741104</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02802599221467972</v>
+        <v>0.04068183153867722</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.02490637823939323</v>
+        <v>0.007705472409725189</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03499139472842216</v>
+        <v>0.1744181960821152</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.002016161335632205</v>
+        <v>0.03780702129006386</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0293552353978157</v>
+        <v>0.02560476586222649</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.009987737983465195</v>
+        <v>0.09309448301792145</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.01222786866128445</v>
+        <v>0.0735686719417572</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.01987685076892376</v>
+        <v>0.06643083691596985</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0003091194666922092</v>
+        <v>0.06154295057058334</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.02254086174070835</v>
+        <v>0.07424073666334152</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.06802942603826523</v>
+        <v>0.1163289770483971</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2567346692085266</v>
+        <v>0.4152416884899139</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.00290478253737092</v>
+        <v>0.004419216886162758</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.05344313755631447</v>
+        <v>0.07844583690166473</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.87667590379715e-05</v>
+        <v>0.05181361734867096</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.03304745629429817</v>
+        <v>0.06972409039735794</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.03523710370063782</v>
+        <v>0.04793737828731537</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.04013529047369957</v>
+        <v>0.1199106127023697</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0325077623128891</v>
+        <v>0.03132486343383789</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.01645457558333874</v>
+        <v>0.06723088026046753</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.05307436361908913</v>
+        <v>0.1500113308429718</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.1002720296382904</v>
+        <v>0.06072834506630898</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.09846484661102295</v>
+        <v>0.02327225171029568</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.07173645496368408</v>
+        <v>0.1971599012613297</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.04226149618625641</v>
+        <v>0.07916957139968872</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.05609842762351036</v>
+        <v>0.0636555403470993</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.05704102665185928</v>
+        <v>0.008881425485014915</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.01525724120438099</v>
+        <v>0.06902000308036804</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.002711623441427946</v>
+        <v>0.05611977353692055</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.06610845029354095</v>
+        <v>0.02958379685878754</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.04647651314735413</v>
+        <v>0.05985556915402412</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.03621954470872879</v>
+        <v>0.03128047659993172</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.09210868179798126</v>
+        <v>0.09109866619110107</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.03721755743026733</v>
+        <v>0.1334110051393509</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.03176429867744446</v>
+        <v>0.0290546678006649</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.02407227270305157</v>
+        <v>0.01883467473089695</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.01021324563771486</v>
+        <v>0.08106676489114761</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.03849933296442032</v>
+        <v>0.08872523158788681</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1203120946884155</v>
+        <v>0.2014120519161224</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.04618481174111366</v>
+        <v>0.03281786665320396</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0217130035161972</v>
+        <v>0.02850805968046188</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0233807135373354</v>
+        <v>0.07645414024591446</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.03047906048595905</v>
+        <v>0.1401617377996445</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.002669197740033269</v>
+        <v>0.01251542381942272</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.03760665655136108</v>
+        <v>0.07837159186601639</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.03289496898651123</v>
+        <v>0.01030850782990456</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.006703987717628479</v>
+        <v>0.02123847603797913</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.05896402522921562</v>
+        <v>0.1086545512080193</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0310296006500721</v>
+        <v>0.01734370179474354</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.04006426781415939</v>
+        <v>0.03488890826702118</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.001099202781915665</v>
+        <v>0.03736279532313347</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02053801715373993</v>
+        <v>0.1073292940855026</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.03050066903233528</v>
+        <v>0.03926728293299675</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.008708592504262924</v>
+        <v>0.01420086249709129</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.02272196859121323</v>
+        <v>0.03093900345265865</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.06709158420562744</v>
+        <v>0.03329191356897354</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.06524068117141724</v>
+        <v>0.1575575023889542</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.01572451740503311</v>
+        <v>0.06246361508965492</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.003859723918139935</v>
+        <v>0.02135867439210415</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.04930970072746277</v>
+        <v>0.1685290783643723</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.0323619581758976</v>
+        <v>0.09029091149568558</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.01065826416015625</v>
+        <v>0.08423227071762085</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.03347605466842651</v>
+        <v>0.04012295603752136</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.01824731566011906</v>
+        <v>0.02779440023005009</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.01105502434074879</v>
+        <v>0.03387906774878502</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.04809563979506493</v>
+        <v>0.10929886251688</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.04174293577671051</v>
+        <v>0.02535237744450569</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.05938299372792244</v>
+        <v>0.03659433871507645</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.004476781934499741</v>
+        <v>0.04618635773658752</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01029285695403814</v>
+        <v>0.1022391021251678</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.03509452566504478</v>
+        <v>0.0440240167081356</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.003651636885479093</v>
+        <v>0.004251081496477127</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.01475814078003168</v>
+        <v>0.0479404404759407</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.02165655419230461</v>
+        <v>0.001110076904296875</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.1697378307580948</v>
+        <v>0.05051276087760925</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.03618751466274261</v>
+        <v>0.1439891904592514</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.08499287068843842</v>
+        <v>0.06977455317974091</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.04502531513571739</v>
+        <v>0.02138702385127544</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01400221325457096</v>
+        <v>0.06612978130578995</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.05965748429298401</v>
+        <v>0.007260141428560019</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.01176902651786804</v>
+        <v>0.1490539461374283</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.03600961714982986</v>
+        <v>0.00231710821390152</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.01003329083323479</v>
+        <v>0.004306829534471035</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0351899154484272</v>
+        <v>0.05956693738698959</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.03240824118256569</v>
+        <v>0.03617685660719872</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.03182734549045563</v>
+        <v>0.1366346329450607</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01913352869451046</v>
+        <v>0.06983699649572372</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.01056179404258728</v>
+        <v>0.1179322600364685</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.02376968786120415</v>
+        <v>0.1233013868331909</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.006378174759447575</v>
+        <v>0.0001388033851981163</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.03347876667976379</v>
+        <v>0.04936523362994194</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.01029854547232389</v>
+        <v>0.05450030416250229</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0272376649081707</v>
+        <v>0.0163370817899704</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.01985087431967258</v>
+        <v>0.1056553721427917</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.03731091693043709</v>
+        <v>0.01008871477097273</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01795145682990551</v>
+        <v>0.06480106711387634</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0238969512283802</v>
+        <v>0.1448818296194077</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.004969182889908552</v>
+        <v>0.06879197806119919</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.04339586570858955</v>
+        <v>0.001966373296454549</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.003440992906689644</v>
+        <v>0.01567907445132732</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.02814793027937412</v>
+        <v>0.04981535673141479</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.02248925529420376</v>
+        <v>0.1350982338190079</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0252064224332571</v>
+        <v>0.031831294298172</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.04427643865346909</v>
+        <v>0.09651302546262741</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.007314782124012709</v>
+        <v>0.002699373755604029</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.02303568460047245</v>
+        <v>0.08617980033159256</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.02941619791090488</v>
+        <v>0.003179236315190792</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.02108777686953545</v>
+        <v>0.02477078512310982</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.009099246934056282</v>
+        <v>0.02876441925764084</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.02717887982726097</v>
+        <v>0.05831331759691238</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01593339815735817</v>
+        <v>0.06703551113605499</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.06529306620359421</v>
+        <v>0.05386907607316971</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.05165745690464973</v>
+        <v>0.06674030423164368</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01203051302582026</v>
+        <v>0.04991487413644791</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.07083003222942352</v>
+        <v>0.04827206581830978</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.02841917611658573</v>
+        <v>0.04030213505029678</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.03213666379451752</v>
+        <v>0.05398096889257431</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.01220402494072914</v>
+        <v>0.02215681411325932</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.01236617937684059</v>
+        <v>0.03744233027100563</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.04397962614893913</v>
+        <v>0.1197822019457817</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0333615243434906</v>
+        <v>0.04414044693112373</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.04816869646310806</v>
+        <v>0.05488458648324013</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.001848381711170077</v>
+        <v>0.03322620689868927</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.01966648176312447</v>
+        <v>0.0776556208729744</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.04115582257509232</v>
+        <v>0.03673001378774643</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.009649251587688923</v>
+        <v>0.004129304550588131</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0215222891420126</v>
+        <v>0.04314199090003967</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.02571537718176842</v>
+        <v>0.1726705580949783</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.01725778728723526</v>
+        <v>0.08803105354309082</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.02384471707046032</v>
+        <v>0.007887445390224457</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.02975050359964371</v>
+        <v>0.06723935902118683</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.01705573685467243</v>
+        <v>0.05666506662964821</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01266677025705576</v>
+        <v>0.0520673543214798</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.009305131621658802</v>
+        <v>0.02744746580719948</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.01301551330834627</v>
+        <v>0.0526430569589138</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.005677762441337109</v>
+        <v>0.1187416762113571</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.03098177164793015</v>
+        <v>0.05680792406201363</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.04916907846927643</v>
+        <v>0.2830502986907959</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.05813020467758179</v>
+        <v>0.1412181407213211</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.03033964335918427</v>
+        <v>0.03860811144113541</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.06454887986183167</v>
+        <v>0.1958651393651962</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.00513944961130619</v>
+        <v>0.2649604082107544</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.05808329954743385</v>
+        <v>0.1291235387325287</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.03887635841965675</v>
+        <v>0.123647078871727</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.01225879695266485</v>
+        <v>0.03750096261501312</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.0445428304374218</v>
+        <v>0.008205128833651543</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.02522752806544304</v>
+        <v>0.06781227886676788</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0131989698857069</v>
+        <v>0.02228013426065445</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.03794548660516739</v>
+        <v>0.04147418215870857</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0190561804920435</v>
+        <v>0.01060126442462206</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.03104242123663425</v>
+        <v>0.03795388713479042</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.09476850181818008</v>
+        <v>0.07991740852594376</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.04135749489068985</v>
+        <v>0.009471183642745018</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.03231958299875259</v>
+        <v>0.01840203627943993</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.009435534477233887</v>
+        <v>0.2925201654434204</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1654987335205078</v>
+        <v>0.5905687212944031</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02313591167330742</v>
+        <v>0.1024680510163307</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05695121735334396</v>
+        <v>0.2317246198654175</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03938447311520576</v>
+        <v>0.5872637629508972</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01685550808906555</v>
+        <v>0.8621578216552734</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01150890160351992</v>
+        <v>0.2959384918212891</v>
       </c>
       <c r="H12" t="n">
-        <v>0.005720283836126328</v>
+        <v>0.541477382183075</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06072047352790833</v>
+        <v>0.2564603090286255</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01101674512028694</v>
+        <v>0.07909268885850906</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1278612315654755</v>
+        <v>0.9179636240005493</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003088942961767316</v>
+        <v>2.591311931610107e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05874904245138168</v>
+        <v>0.08768726885318756</v>
       </c>
       <c r="N12" t="n">
-        <v>0.06397926062345505</v>
+        <v>0.6813504695892334</v>
       </c>
       <c r="O12" t="n">
-        <v>0.03087871894240379</v>
+        <v>0.8890774250030518</v>
       </c>
       <c r="P12" t="n">
-        <v>0.01697357557713985</v>
+        <v>0.3902167975902557</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02107786387205124</v>
+        <v>0.03812544047832489</v>
       </c>
       <c r="R12" t="n">
-        <v>0.04568519070744514</v>
+        <v>0.2275108247995377</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001641370821744204</v>
+        <v>0.1735878884792328</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03550061583518982</v>
+        <v>0.1285114586353302</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02724580839276314</v>
+        <v>0.03698878735303879</v>
       </c>
       <c r="V12" t="n">
-        <v>0.02323462441563606</v>
+        <v>0.4981204271316528</v>
       </c>
       <c r="W12" t="n">
-        <v>0.007094331551343203</v>
+        <v>0.404314398765564</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0294290017336607</v>
+        <v>0.1918535530567169</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.006208015605807304</v>
+        <v>0.0217369943857193</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.00543100293725729</v>
+        <v>0.0853707417845726</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0128085920587182</v>
+        <v>0.2256396263837814</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.01184884086251259</v>
+        <v>0.1398344486951828</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.02318303287029266</v>
+        <v>0.3135760128498077</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.001720418804325163</v>
+        <v>0.1791064143180847</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.004811182152479887</v>
+        <v>0.2548255920410156</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.003645121119916439</v>
+        <v>0.299499124288559</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01946846954524517</v>
+        <v>0.2362212240695953</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.008560458198189735</v>
+        <v>0.008720108307898045</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.02528846450150013</v>
+        <v>0.5800244212150574</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.01167620904743671</v>
+        <v>0.01124555431306362</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.01619118079543114</v>
+        <v>0.06594886630773544</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01695339195430279</v>
+        <v>0.4562487602233887</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.01223783195018768</v>
+        <v>0.100946269929409</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.002934681251645088</v>
+        <v>0.2611992955207825</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.01583596132695675</v>
+        <v>0.274121880531311</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.01405506953597069</v>
+        <v>0.1469235569238663</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.01102979574352503</v>
+        <v>0.07438448816537857</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.001312526408582926</v>
+        <v>0.1880858838558197</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.006158633157610893</v>
+        <v>0.08851509541273117</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.01320892944931984</v>
+        <v>0.1507120430469513</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1326406747102737</v>
+        <v>1.713827729225159</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.003550310153514147</v>
+        <v>0.0694139376282692</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.002938072197139263</v>
+        <v>0.04169043153524399</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.006203832104802132</v>
+        <v>0.1453937292098999</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.008187810890376568</v>
+        <v>0.422200620174408</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.01300016418099403</v>
+        <v>0.1393231451511383</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.002431946806609631</v>
+        <v>0.1068544387817383</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.01374341733753681</v>
+        <v>0.03276333212852478</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.00614741537719965</v>
+        <v>0.3556618392467499</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0395868606865406</v>
+        <v>0.5685091018676758</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.02362190932035446</v>
+        <v>0.2561619877815247</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.009794272482395172</v>
+        <v>0.2668891549110413</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.05800408497452736</v>
+        <v>0.6061490774154663</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.03732380270957947</v>
+        <v>0.08045960962772369</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.005385803058743477</v>
+        <v>0.1116025373339653</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.02384141460061073</v>
+        <v>0.2818957567214966</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0204005241394043</v>
+        <v>0.01149160694330931</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.01696064695715904</v>
+        <v>0.09200658649206161</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.03850948065519333</v>
+        <v>0.4032044410705566</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.01641609892249107</v>
+        <v>0.02465806901454926</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.002114427275955677</v>
+        <v>0.2811219096183777</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.06538873165845871</v>
+        <v>0.3686436414718628</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.03107872419059277</v>
+        <v>0.2727931439876556</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0001273166853934526</v>
+        <v>0.7385349869728088</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.01550238393247128</v>
+        <v>0.1002125069499016</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.003987449221313</v>
+        <v>0.007814282551407814</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.008718661963939667</v>
+        <v>0.08511783927679062</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.07606396824121475</v>
+        <v>0.8458253741264343</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.01228503603488207</v>
+        <v>0.06690120697021484</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01475331000983715</v>
+        <v>0.507464587688446</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0138431778177619</v>
+        <v>0.3447267711162567</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.03540617227554321</v>
+        <v>0.3474225103855133</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0199726615101099</v>
+        <v>0.124004915356636</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.002530094236135483</v>
+        <v>0.06851308047771454</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.02142244949936867</v>
+        <v>0.2672790586948395</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.001097565283998847</v>
+        <v>0.0509752631187439</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.03199020773172379</v>
+        <v>0.3330326676368713</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.00149401999078691</v>
+        <v>0.04676754400134087</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01286265440285206</v>
+        <v>0.08530633896589279</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.005341649986803532</v>
+        <v>0.0756608173251152</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.001052329316735268</v>
+        <v>0.1801290512084961</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0008884358685463667</v>
+        <v>0.1722663640975952</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.00592187000438571</v>
+        <v>0.08194708824157715</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.01741365529596806</v>
+        <v>0.03871554881334305</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0423957034945488</v>
+        <v>0.3957688808441162</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.05845068022608757</v>
+        <v>0.9391912221908569</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.001598531380295753</v>
+        <v>0.3539136648178101</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.01207342185080051</v>
+        <v>0.5147774815559387</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.02619636431336403</v>
+        <v>0.1271370053291321</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.007675386965274811</v>
+        <v>0.06888556480407715</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.01407915260642767</v>
+        <v>0.352601021528244</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.03944699093699455</v>
+        <v>0.1230432242155075</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.002909226808696985</v>
+        <v>0.03018964268267155</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.001168725895695388</v>
+        <v>0.1314357817173004</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.02622869424521923</v>
+        <v>0.2621767818927765</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.007477991748601198</v>
+        <v>0.05412472784519196</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.01574964821338654</v>
+        <v>0.007423979230225086</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.000706216786056757</v>
+        <v>0.0571398101747036</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.00614483468234539</v>
+        <v>0.1611524671316147</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.00176790077239275</v>
+        <v>0.07980865240097046</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0004983753897249699</v>
+        <v>0.04105251654982567</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.01413429621607065</v>
+        <v>0.04130681976675987</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.03093559294939041</v>
+        <v>0.4413924217224121</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.09046592563390732</v>
+        <v>0.0894305408000946</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.01874489895999432</v>
+        <v>0.03305850923061371</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.05677040666341782</v>
+        <v>0.4652249217033386</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0003849158529192209</v>
+        <v>0.07002043724060059</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.004898058250546455</v>
+        <v>0.1445011049509048</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.04707771167159081</v>
+        <v>0.1769275814294815</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.01409166399389505</v>
+        <v>0.582529604434967</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.02024854719638824</v>
+        <v>0.1115725040435791</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.01702472940087318</v>
+        <v>0.06088569760322571</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.01774141937494278</v>
+        <v>0.054033312946558</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.01670050248503685</v>
+        <v>0.1026191264390945</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.02168841287493706</v>
+        <v>0.3326444923877716</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.004098138306289911</v>
+        <v>0.122089721262455</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.001814628718420863</v>
+        <v>0.07311979681253433</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.02912038192152977</v>
+        <v>0.01377834752202034</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.002899340353906155</v>
+        <v>0.1201349869370461</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0007162317633628845</v>
+        <v>0.02983924560248852</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.01047408021986485</v>
+        <v>0.003019951283931732</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01211248617619276</v>
+        <v>0.3648949861526489</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.01327461842447519</v>
+        <v>0.2844272255897522</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.01608615182340145</v>
+        <v>0.145902082324028</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.02155734412372112</v>
+        <v>0.325437605381012</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.01000484265387058</v>
+        <v>0.2568794190883636</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.01096601411700249</v>
+        <v>0.06650266051292419</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.01384737156331539</v>
+        <v>0.1963001489639282</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.001423480920493603</v>
+        <v>0.1986400038003922</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.004596534185111523</v>
+        <v>0.1161368042230606</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.005325509700924158</v>
+        <v>0.1041729673743248</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.001683223759755492</v>
+        <v>0.08748756349086761</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.009904425591230392</v>
+        <v>0.132892370223999</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.006314997561275959</v>
+        <v>0.07738287001848221</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.00335905933752656</v>
+        <v>0.2208753079175949</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.007341668009757996</v>
+        <v>0.05008359998464584</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.005730561912059784</v>
+        <v>0.05546782165765762</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.01833922043442726</v>
+        <v>0.04121432453393936</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01461940631270409</v>
+        <v>0.06566332280635834</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.01544821914285421</v>
+        <v>0.2171568870544434</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.00991036556661129</v>
+        <v>0.1254486739635468</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01479736436158419</v>
+        <v>0.02755587548017502</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.01451338827610016</v>
+        <v>0.07541017979383469</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0332476794719696</v>
+        <v>0.01312002632766962</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.01028889045119286</v>
+        <v>0.1850890964269638</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.01560413092374802</v>
+        <v>0.2085253894329071</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.007943007163703442</v>
+        <v>0.2055969387292862</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0006860475987195969</v>
+        <v>0.08628277480602264</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.02985469251871109</v>
+        <v>0.3679102659225464</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.003482801839709282</v>
+        <v>0.07686400413513184</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.01361777819693089</v>
+        <v>0.007035487331449986</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.001538904965855181</v>
+        <v>0.0553499311208725</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.01057565957307816</v>
+        <v>0.1881926357746124</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.004281424451619387</v>
+        <v>0.1835079193115234</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.007248965557664633</v>
+        <v>0.06679931282997131</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.01316536962985992</v>
+        <v>0.08040698617696762</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.009381962940096855</v>
+        <v>0.1870361566543579</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01824504137039185</v>
+        <v>0.2441553175449371</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.003165796399116516</v>
+        <v>0.06392969191074371</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01290556974709034</v>
+        <v>0.3272925615310669</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.01384084112942219</v>
+        <v>0.2176339328289032</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.005469937808811665</v>
+        <v>0.1373917460441589</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.008877046406269073</v>
+        <v>0.1310687959194183</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.01277503930032253</v>
+        <v>0.3587176203727722</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.02343548275530338</v>
+        <v>0.1399150937795639</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.006936667487025261</v>
+        <v>0.2523229122161865</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.01925785467028618</v>
+        <v>0.3653584718704224</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.02948459051549435</v>
+        <v>0.1095646470785141</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01016547717154026</v>
+        <v>0.129127100110054</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.02491598576307297</v>
+        <v>0.5064143538475037</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01937564462423325</v>
+        <v>0.2991178333759308</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.003535492811352015</v>
+        <v>0.01809904910624027</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.008955540135502815</v>
+        <v>0.3829464018344879</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.01029594801366329</v>
+        <v>0.1155912950634956</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.005556066520512104</v>
+        <v>0.05591946467757225</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.03760833293199539</v>
+        <v>0.04993431642651558</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.01808054000139236</v>
+        <v>0.1419531553983688</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.02637334913015366</v>
+        <v>0.1093208789825439</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.039139024913311</v>
+        <v>0.2511433959007263</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.03517481312155724</v>
+        <v>0.266922801733017</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.02650006301701069</v>
+        <v>0.03479643911123276</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.006836568005383015</v>
+        <v>0.2239859104156494</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.006745249964296818</v>
+        <v>0.03526266664266586</v>
       </c>
     </row>
     <row r="13">
@@ -7827,1140 +7827,1140 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.02345351129770279</v>
+        <v>0.193108081817627</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6453219652175903</v>
+        <v>0.3686923384666443</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7096957564353943</v>
+        <v>0.3457954227924347</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2792933285236359</v>
+        <v>0.07699067890644073</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4194515943527222</v>
+        <v>0.1572141647338867</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2336542308330536</v>
+        <v>0.07776352763175964</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2325236052274704</v>
+        <v>0.1523085236549377</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3230859339237213</v>
+        <v>0.1746021658182144</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4972466826438904</v>
+        <v>0.1529038101434708</v>
       </c>
       <c r="J14" t="n">
-        <v>0.07064009457826614</v>
+        <v>0.1265420913696289</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5609126091003418</v>
+        <v>0.3907793760299683</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4349837303161621</v>
+        <v>0.334936261177063</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2316285818815231</v>
+        <v>0.07442048937082291</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6650440692901611</v>
+        <v>0.2021284997463226</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3385622501373291</v>
+        <v>0.003456249833106995</v>
       </c>
       <c r="P14" t="n">
-        <v>0.07721459865570068</v>
+        <v>0.1986976265907288</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1804855465888977</v>
+        <v>0.03578302264213562</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4542455077171326</v>
+        <v>0.1392160803079605</v>
       </c>
       <c r="S14" t="n">
-        <v>0.04194013029336929</v>
+        <v>0.1142082735896111</v>
       </c>
       <c r="T14" t="n">
-        <v>0.09040634334087372</v>
+        <v>0.08589695394039154</v>
       </c>
       <c r="U14" t="n">
-        <v>0.03832217678427696</v>
+        <v>0.07497267425060272</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2679429352283478</v>
+        <v>0.1344297677278519</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1643761992454529</v>
+        <v>0.03177416324615479</v>
       </c>
       <c r="X14" t="n">
-        <v>0.09916504472494125</v>
+        <v>0.00466989167034626</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.02913465537130833</v>
+        <v>0.001310070510953665</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1395377814769745</v>
+        <v>0.05263907834887505</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0571906603872776</v>
+        <v>0.1305485516786575</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.1114106103777885</v>
+        <v>0.1595418900251389</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.195542648434639</v>
+        <v>0.05558183044195175</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0147680975496769</v>
+        <v>0.06057747825980186</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.02424462139606476</v>
+        <v>0.2030996680259705</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2129938453435898</v>
+        <v>0.07887708395719528</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.3248198330402374</v>
+        <v>0.1389499306678772</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.04516446590423584</v>
+        <v>0.1094610467553139</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.163116842508316</v>
+        <v>0.2925355732440948</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.1084271818399429</v>
+        <v>0.1934172064065933</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.001495122909545898</v>
+        <v>0.07768517732620239</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.3419173955917358</v>
+        <v>0.227605402469635</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0906333327293396</v>
+        <v>0.01274985633790493</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.09394250810146332</v>
+        <v>0.03758221864700317</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.04995923489332199</v>
+        <v>0.2897206544876099</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.2554556131362915</v>
+        <v>0.08463479578495026</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0215739868581295</v>
+        <v>0.006429718807339668</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.147820457816124</v>
+        <v>0.09294986724853516</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.1100473329424858</v>
+        <v>0.03693745285272598</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.2037151753902435</v>
+        <v>0.01890797913074493</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.4518331289291382</v>
+        <v>0.5341518521308899</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.4423260092735291</v>
+        <v>0.0893281027674675</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1007295697927475</v>
+        <v>0.03849607706069946</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1326229572296143</v>
+        <v>0.04284824430942535</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.1508183777332306</v>
+        <v>0.08814908564090729</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.04342198371887207</v>
+        <v>0.008605705574154854</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.1962376683950424</v>
+        <v>0.1031248718500137</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0215420313179493</v>
+        <v>0.02564674615859985</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.06647021323442459</v>
+        <v>0.1259166151285172</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.1005230098962784</v>
+        <v>0.3426176309585571</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.08206226676702499</v>
+        <v>0.2273373007774353</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.2252490371465683</v>
+        <v>0.03188581764698029</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.5048380494117737</v>
+        <v>0.3065800070762634</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.1981481313705444</v>
+        <v>0.02175893448293209</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.07828515022993088</v>
+        <v>0.03565386310219765</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.09496176242828369</v>
+        <v>0.05509386211633682</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.2516157031059265</v>
+        <v>0.01490815915167332</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.1628180295228958</v>
+        <v>0.05197742581367493</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1331343948841095</v>
+        <v>0.0559692494571209</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.07415346801280975</v>
+        <v>0.05925338715314865</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.139643594622612</v>
+        <v>0.1061326116323471</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1408426761627197</v>
+        <v>0.03646160289645195</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.1213088408112526</v>
+        <v>0.009410478174686432</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.1762029528617859</v>
+        <v>0.1833078563213348</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.1422254294157028</v>
+        <v>0.0506356842815876</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.1501069217920303</v>
+        <v>0.1009345352649689</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.1587382704019547</v>
+        <v>0.01189475506544113</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.2763913571834564</v>
+        <v>0.4550589621067047</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.3669516444206238</v>
+        <v>0.0539466068148613</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.1131802797317505</v>
+        <v>0.05788098275661469</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.09706098586320877</v>
+        <v>0.03471910580992699</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.03764286637306213</v>
+        <v>0.096380814909935</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.001098312437534332</v>
+        <v>0.09932716935873032</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.1522375345230103</v>
+        <v>0.05236361175775528</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.08348458260297775</v>
+        <v>0.1138598173856735</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.02168387174606323</v>
+        <v>0.05711463093757629</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.09847924113273621</v>
+        <v>0.1811253428459167</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.07836107909679413</v>
+        <v>0.09117588400840759</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.1730492860078812</v>
+        <v>0.05473047867417336</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.1185449734330177</v>
+        <v>0.005099285393953323</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.006485906429588795</v>
+        <v>0.01192442048341036</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.02887436561286449</v>
+        <v>0.001284163678064942</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.1011354476213455</v>
+        <v>0.0455586276948452</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.08646170794963837</v>
+        <v>0.03077879548072815</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.07018815726041794</v>
+        <v>0.2122171819210052</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.04500357061624527</v>
+        <v>0.2097317278385162</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.03042555600404739</v>
+        <v>0.1082712188363075</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.3730984032154083</v>
+        <v>0.1567974388599396</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.3685989379882812</v>
+        <v>0.1703903079032898</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.1211558729410172</v>
+        <v>0.07489325851202011</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.1971451342105865</v>
+        <v>0.1326525509357452</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.02020080573856831</v>
+        <v>0.0963624119758606</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.1126604452729225</v>
+        <v>0.05858401209115982</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.03742364048957825</v>
+        <v>0.07663092017173767</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.05442789196968079</v>
+        <v>0.1567298769950867</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.07718496024608612</v>
+        <v>0.08983076363801956</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.1085128262639046</v>
+        <v>0.0248764380812645</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.1372154653072357</v>
+        <v>0.01495135575532913</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.05461562052369118</v>
+        <v>0.02169365063309669</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.005327502265572548</v>
+        <v>0.004674657247960567</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.09075944870710373</v>
+        <v>0.01823639124631882</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.1284291744232178</v>
+        <v>0.07168527692556381</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.1474717557430267</v>
+        <v>0.1585282683372498</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.02659247443079948</v>
+        <v>0.03543868660926819</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.09208687394857407</v>
+        <v>0.06220638006925583</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.3319658041000366</v>
+        <v>0.105969674885273</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.2468218058347702</v>
+        <v>0.07877457141876221</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.3220728039741516</v>
+        <v>0.2556296288967133</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.1045227944850922</v>
+        <v>0.06058019772171974</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.3287371098995209</v>
+        <v>0.05125262588262558</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.06079732999205589</v>
+        <v>0.164070650935173</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0999412015080452</v>
+        <v>0.05671962350606918</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0455370768904686</v>
+        <v>0.08047693967819214</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.1654369533061981</v>
+        <v>0.08217339962720871</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.1943707019090652</v>
+        <v>0.07503753900527954</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.116726815700531</v>
+        <v>0.03929547965526581</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.138760432600975</v>
+        <v>0.09172908961772919</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.07471740245819092</v>
+        <v>0.05732176452875137</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.1896104663610458</v>
+        <v>0.008364251814782619</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.1764458268880844</v>
+        <v>0.0313844121992588</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.08676241338253021</v>
+        <v>0.02983323112130165</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.04153328761458397</v>
+        <v>0.1238928139209747</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.1604411751031876</v>
+        <v>0.1086530387401581</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.08224180340766907</v>
+        <v>0.008287221193313599</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.05408944562077522</v>
+        <v>0.08422309905290604</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.2175315618515015</v>
+        <v>0.1237246841192245</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.04919444024562836</v>
+        <v>0.01553876977413893</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.1176154240965843</v>
+        <v>0.0796314924955368</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.06947328150272369</v>
+        <v>0.1473711282014847</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.04952916875481606</v>
+        <v>0.02114132419228554</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.05985576659440994</v>
+        <v>0.06897445768117905</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0262238122522831</v>
+        <v>0.03760793805122375</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.08387784659862518</v>
+        <v>0.02067680284380913</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.2081483155488968</v>
+        <v>0.01104874908924103</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.1290984898805618</v>
+        <v>0.06224770098924637</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.07449747622013092</v>
+        <v>0.04451283439993858</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.05114135146141052</v>
+        <v>0.01792071014642715</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.149025946855545</v>
+        <v>0.01552168652415276</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.03307342156767845</v>
+        <v>0.08460436016321182</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.07104183733463287</v>
+        <v>0.1466713398694992</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0543711744248867</v>
+        <v>0.0059532281011343</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.03924013301730156</v>
+        <v>0.08600844442844391</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1029595583677292</v>
+        <v>0.01849523931741714</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.03187540918588638</v>
+        <v>0.1096628084778786</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.1151455193758011</v>
+        <v>0.09874775260686874</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.1471349895000458</v>
+        <v>0.03556053712964058</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.3903762400150299</v>
+        <v>0.0002299612388014793</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.02591131627559662</v>
+        <v>0.06341373920440674</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.07207915931940079</v>
+        <v>0.1950190812349319</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0694158673286438</v>
+        <v>0.08306768536567688</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.1682246625423431</v>
+        <v>0.01513120159506798</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.130410298705101</v>
+        <v>0.02493313141167164</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.06678958237171173</v>
+        <v>0.03633350133895874</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.02198694832623005</v>
+        <v>0.009129233658313751</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.1377829909324646</v>
+        <v>0.01363316830247641</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.05775608122348785</v>
+        <v>0.0668368935585022</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0494057722389698</v>
+        <v>0.01123419776558876</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.1277034729719162</v>
+        <v>0.03966312855482101</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.1425295770168304</v>
+        <v>0.04029949754476547</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.01750283688306808</v>
+        <v>0.0738823190331459</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.1012608483433723</v>
+        <v>0.07168777287006378</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.04219163209199905</v>
+        <v>0.01301651541143656</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.2722724080085754</v>
+        <v>0.003682047827169299</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.05558256804943085</v>
+        <v>0.08249709755182266</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.1378756165504456</v>
+        <v>0.02015640586614609</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.116241917014122</v>
+        <v>0.1375143975019455</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.01377143152058125</v>
+        <v>0.2021583616733551</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.2095647603273392</v>
+        <v>0.06342091411352158</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.3020946681499481</v>
+        <v>0.05991051718592644</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.1505401283502579</v>
+        <v>0.1344491839408875</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.04924401640892029</v>
+        <v>0.07576699554920197</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.2235341966152191</v>
+        <v>0.09758583456277847</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.2941326498985291</v>
+        <v>0.0163511261343956</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.07882116734981537</v>
+        <v>0.1895041763782501</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.08128563314676285</v>
+        <v>0.139036238193512</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.1082967221736908</v>
+        <v>0.0512935183942318</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.06382989138364792</v>
+        <v>0.004215765744447708</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.03443377465009689</v>
+        <v>0.002321962267160416</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.07748901098966599</v>
+        <v>0.03315376862883568</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.1791875511407852</v>
+        <v>0.001450706273317337</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.2217925041913986</v>
+        <v>0.07331383228302002</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.4605424106121063</v>
+        <v>0.03170513361692429</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.02204828523099422</v>
+        <v>0.04675914347171783</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.002569583943113685</v>
+        <v>0.001172390300780535</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02850898914039135</v>
+        <v>0.004090039525181055</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003083593212068081</v>
+        <v>0.001717216684482992</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01868777722120285</v>
+        <v>0.001491100527346134</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002963480306789279</v>
+        <v>0.003400796093046665</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05699427798390388</v>
+        <v>0.009264673106372356</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01401686854660511</v>
+        <v>0.001750010880641639</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02624247409403324</v>
+        <v>0.005803085397928953</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01163212116807699</v>
+        <v>0.001811868045479059</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001530960667878389</v>
+        <v>0.0003988355747424066</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02185716293752193</v>
+        <v>0.007292282767593861</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0002782726951409131</v>
+        <v>0.003276150207966566</v>
       </c>
       <c r="M15" t="n">
-        <v>0.006425302475690842</v>
+        <v>0.003800940699875355</v>
       </c>
       <c r="N15" t="n">
-        <v>0.004010353237390518</v>
+        <v>0.005213000811636448</v>
       </c>
       <c r="O15" t="n">
-        <v>0.04531934857368469</v>
+        <v>0.01195365935564041</v>
       </c>
       <c r="P15" t="n">
-        <v>0.01471399515867233</v>
+        <v>0.0006181729258969426</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01503662951290607</v>
+        <v>0.003657519351691008</v>
       </c>
       <c r="R15" t="n">
-        <v>0.008377261459827423</v>
+        <v>0.004170429892838001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001045692362822592</v>
+        <v>0.0003170457493979484</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0004044858505949378</v>
+        <v>0.001674592029303312</v>
       </c>
       <c r="U15" t="n">
-        <v>0.004433019552379847</v>
+        <v>0.0006399929989129305</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01337719149887562</v>
+        <v>0.001859102747403085</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0148240439593792</v>
+        <v>0.000901569495908916</v>
       </c>
       <c r="X15" t="n">
-        <v>0.006680633407086134</v>
+        <v>0.001225850428454578</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0004476490430533886</v>
+        <v>0.00111913587898016</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.003281424986198545</v>
+        <v>0.00154749141074717</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.002074161311611533</v>
+        <v>0.0003246915875934064</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.003738706931471825</v>
+        <v>0.0008928184979595244</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.002971103880554438</v>
+        <v>0.0007502046646550298</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.00770763261243701</v>
+        <v>9.005039464682341e-05</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.00523051805794239</v>
+        <v>0.001879658084362745</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.00047832983545959</v>
+        <v>0.003993967548012733</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0008693449781276286</v>
+        <v>0.0005435532075352967</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.002094977768138051</v>
+        <v>0.0002616870333440602</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.004438711330294609</v>
+        <v>0.00362424086779356</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0008835436310619116</v>
+        <v>0.0008143376326188445</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.004728421568870544</v>
+        <v>0.001244986779056489</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.001145067391917109</v>
+        <v>0.001544610247947276</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.002141284057870507</v>
+        <v>0.0007884419756010175</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.007427423726767302</v>
+        <v>0.0007436517626047134</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.006668839603662491</v>
+        <v>0.0007993284380063415</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.01154276262968779</v>
+        <v>0.001425601774826646</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.001831232337281108</v>
+        <v>0.001761583960615098</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.004415021277964115</v>
+        <v>0.001906302524730563</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.001225333311595023</v>
+        <v>0.0001835432485677302</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.006873431149870157</v>
+        <v>0.000178114918526262</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.01633920893073082</v>
+        <v>0.01492810808122158</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.0003923343028873205</v>
+        <v>0.0003052265965379775</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.01161670498549938</v>
+        <v>0.0001382559712510556</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.00985649973154068</v>
+        <v>0.000400250602979213</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.03399721905589104</v>
+        <v>0.008282940834760666</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.008017770946025848</v>
+        <v>0.001463674940168858</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.01110705826431513</v>
+        <v>0.001730555552057922</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.006886866874992847</v>
+        <v>0.0003489718947093934</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.459187716245651e-06</v>
+        <v>0.001142144086770713</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.0003161332570016384</v>
+        <v>0.005529236048460007</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0006245844997465611</v>
+        <v>0.0007116800989024341</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.01571350544691086</v>
+        <v>0.00191785185597837</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.01077993772923946</v>
+        <v>0.002746042562648654</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.01442893128842115</v>
+        <v>0.0006994347204454243</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.002377723809331656</v>
+        <v>0.001360884518362582</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.004089370369911194</v>
+        <v>0.002955396194010973</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.003732845885679126</v>
+        <v>0.0001509869180154055</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0006306599825620651</v>
+        <v>0.0006024910253472626</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.01019048690795898</v>
+        <v>0.005031545180827379</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.005762821994721889</v>
+        <v>0.002388688270002604</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.006268588826060295</v>
+        <v>0.0007979835500009358</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.003019063267856836</v>
+        <v>0.003166582202538848</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.004234118852764368</v>
+        <v>0.0003677038475871086</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.001908090431243181</v>
+        <v>0.002880173735320568</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.01009924057871103</v>
+        <v>0.001249083899892867</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.009587056003510952</v>
+        <v>0.002221744041889906</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.001160189975053072</v>
+        <v>1.939586945809424e-05</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.01166814845055342</v>
+        <v>0.006393971387296915</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.002111339475959539</v>
+        <v>0.0002706852101255208</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.007879175245761871</v>
+        <v>7.146201096475124e-05</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.005952670238912106</v>
+        <v>0.0003472979296930134</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.01672711595892906</v>
+        <v>0.004490557126700878</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.002058318816125393</v>
+        <v>0.00171074690297246</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.004388038069009781</v>
+        <v>0.001388429547660053</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.001710581826046109</v>
+        <v>0.000901390565559268</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.001529157045297325</v>
+        <v>0.0003136985469609499</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.003296010196208954</v>
+        <v>0.00163720129057765</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.0003136290470138192</v>
+        <v>0.001166002592071891</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.0005396581254899502</v>
+        <v>0.0002840430825017393</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.001710961223579943</v>
+        <v>0.001380128553137183</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.008712276816368103</v>
+        <v>0.002148601925000548</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.00566455302760005</v>
+        <v>0.00114639790263027</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.007246583234518766</v>
+        <v>9.882589802145958e-05</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.002309055998921394</v>
+        <v>0.0005571115761995316</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.001810156041756272</v>
+        <v>0.00193443859461695</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.007857039570808411</v>
+        <v>0.006195499561727047</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.001891831401735544</v>
+        <v>0.001575143774971366</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.008815895766019821</v>
+        <v>0.002025803085416555</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.02049429900944233</v>
+        <v>0.0003701690002344549</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.003143662121146917</v>
+        <v>0.001949501573108137</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.003799735801294446</v>
+        <v>0.0005132776568643749</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.006721134297549725</v>
+        <v>0.0002455745707266033</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.004726492799818516</v>
+        <v>0.000417259696405381</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.0003123446949757636</v>
+        <v>0.0009054702240973711</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.003471231320872903</v>
+        <v>0.001372307306155562</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.0005750884301960468</v>
+        <v>0.0012251470470801</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.001358745386824012</v>
+        <v>0.0008609445067122579</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.001089103287085891</v>
+        <v>0.001427690731361508</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01067003514617682</v>
+        <v>0.002582273911684752</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.00490102544426918</v>
+        <v>0.0003944872296415269</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.01052950415760279</v>
+        <v>0.0003282942343503237</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.004284956492483616</v>
+        <v>0.0003346582234371454</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.001879997784271836</v>
+        <v>0.0008740733610466123</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.01569594442844391</v>
+        <v>0.001985229551792145</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.0002156617119908333</v>
+        <v>0.0001982598332688212</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.01682635024189949</v>
+        <v>0.0001410436234436929</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.004416777286678553</v>
+        <v>0.0002065770095214248</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.008508089929819107</v>
+        <v>0.0006655193865299225</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.000536804087460041</v>
+        <v>0.001344837248325348</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.01590597257018089</v>
+        <v>0.0019218516536057</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.004531852435320616</v>
+        <v>0.002407853957265615</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.004693917464464903</v>
+        <v>0.0009314162889495492</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.0006796298548579216</v>
+        <v>0.001767304027453065</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.001036143046803772</v>
+        <v>0.001139907632023096</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.00863143615424633</v>
+        <v>0.001821701414883137</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.008781984448432922</v>
+        <v>0.001607369515113533</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.01247057411819696</v>
+        <v>0.00213279202580452</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.008754235692322254</v>
+        <v>0.0005776513135060668</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.002363820327445865</v>
+        <v>0.001007066923193634</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.001396854873746634</v>
+        <v>0.00270993635058403</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.002106660977005959</v>
+        <v>0.0006781116826459765</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.003364936448633671</v>
+        <v>0.003029892686754465</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.002207541838288307</v>
+        <v>0.001135942991822958</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.0003765970759559423</v>
+        <v>8.544139564037323e-05</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.001399342436343431</v>
+        <v>0.0003273165784776211</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.003415236249566078</v>
+        <v>0.000921374186873436</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.003783621359616518</v>
+        <v>0.0002252098347526044</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.005820523016154766</v>
+        <v>0.002700590528547764</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.006948141381144524</v>
+        <v>0.001023669727146626</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.002136814640834928</v>
+        <v>7.338948489632457e-05</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0007979366928339005</v>
+        <v>0.000217116394196637</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.002222395269200206</v>
+        <v>0.001152386888861656</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.01268661580979824</v>
+        <v>0.0007678628899157047</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.001474079908803105</v>
+        <v>0.001314066001214087</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.002615179866552353</v>
+        <v>0.0001045117969624698</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.002182511612772942</v>
+        <v>0.0005288606625981629</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.007320595905184746</v>
+        <v>0.000739732407964766</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.003687880467623472</v>
+        <v>0.0003269383159931749</v>
       </c>
       <c r="EO15" t="n">
-        <v>8.908573363441974e-06</v>
+        <v>0.00061758141964674</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.003198607126250863</v>
+        <v>0.001112506259232759</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.004504360258579254</v>
+        <v>0.0008126838365569711</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.007186341099441051</v>
+        <v>0.0001009052211884409</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.0006004651077091694</v>
+        <v>0.001494978438131511</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.0009334840578958392</v>
+        <v>0.0008879007073119283</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.000669712433591485</v>
+        <v>0.001167761860415339</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.01213408913463354</v>
+        <v>0.0003148026880808175</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.009557468816637993</v>
+        <v>0.0005965405725874007</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.0009652199223637581</v>
+        <v>0.0007773346151225269</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.002643762854859233</v>
+        <v>0.002064011758193374</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.000134208588860929</v>
+        <v>0.0007636318914592266</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.0004264092422090471</v>
+        <v>0.0008545033633708954</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.000501139264088124</v>
+        <v>0.0007648971513845026</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.008091969415545464</v>
+        <v>0.002387834945693612</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.005711064673960209</v>
+        <v>0.001247267005965114</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.008280178532004356</v>
+        <v>0.00021004443988204</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.003434610553085804</v>
+        <v>0.000198673689737916</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.0004663756117224693</v>
+        <v>0.000440693402197212</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.008038723841309547</v>
+        <v>0.001291701104491949</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.006116928067058325</v>
+        <v>0.0007022516801953316</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.007167419884353876</v>
+        <v>0.00266023282893002</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.003881064709275961</v>
+        <v>0.001774459728039801</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.009885258972644806</v>
+        <v>0.002061612205579877</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.000485082040540874</v>
+        <v>0.001298567047342658</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.0008536179084330797</v>
+        <v>0.0006217734189704061</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.003385864198207855</v>
+        <v>0.003256837837398052</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.005637664347887039</v>
+        <v>0.00262406887486577</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.004550040233880281</v>
+        <v>0.002810647245496511</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.008107404224574566</v>
+        <v>0.002028043614700437</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.003258969634771347</v>
+        <v>0.004033978562802076</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.009428140707314014</v>
+        <v>0.005646471865475178</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.009252934716641903</v>
+        <v>0.0003832934307865798</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.003003839636221528</v>
+        <v>0.001021372270770371</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.009769473224878311</v>
+        <v>0.003239503595978022</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.01062082871794701</v>
+        <v>0.002454789821058512</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.0004588047158904374</v>
+        <v>0.0004658268881030381</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.001477666548453271</v>
+        <v>9.152534767054021e-05</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.006235009059309959</v>
+        <v>0.001857222523540258</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.01060023903846741</v>
+        <v>0.0009508337825536728</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.02583795972168446</v>
+        <v>0.002306345151737332</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.001338962931185961</v>
+        <v>0.0003132495912723243</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.01005999837070704</v>
+        <v>0.002560058142989874</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.007206459529697895</v>
+        <v>0.0003741665568668395</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.004023682326078415</v>
+        <v>0.0002440769167151302</v>
       </c>
     </row>
   </sheetData>
